--- a/Ground Truth/ground_truth_hvac.xlsx
+++ b/Ground Truth/ground_truth_hvac.xlsx
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="M2" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="N2" t="n">
         <v>0.7</v>
@@ -577,7 +577,7 @@
         <v>0.74</v>
       </c>
       <c r="P2" t="n">
-        <v>0.797</v>
+        <v>0.7255</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="M3" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
@@ -651,7 +651,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8835</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="M4" t="n">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="N4" t="n">
         <v>0.7</v>
@@ -725,7 +725,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8365</v>
+        <v>0.762</v>
       </c>
       <c r="Q4" t="n">
         <v>2</v>
@@ -787,10 +787,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0.78</v>
@@ -799,19 +799,19 @@
         <v>0.63</v>
       </c>
       <c r="P5" t="n">
-        <v>0.884</v>
+        <v>0.9005</v>
       </c>
       <c r="Q5" t="n">
         <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
@@ -873,19 +873,19 @@
         <v>0.63</v>
       </c>
       <c r="P6" t="n">
-        <v>0.912</v>
+        <v>0.9445</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>3.77</v>
+        <v>0.18</v>
       </c>
       <c r="S6" t="n">
-        <v>0.72</v>
+        <v>0.03</v>
       </c>
       <c r="T6" t="n">
-        <v>3.84</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="7">
@@ -935,10 +935,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
         <v>0.78</v>
@@ -947,19 +947,19 @@
         <v>0.63</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8515</v>
+        <v>0.9005</v>
       </c>
       <c r="Q7" t="n">
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>4.13</v>
+        <v>0.55</v>
       </c>
       <c r="S7" t="n">
-        <v>0.79</v>
+        <v>0.1</v>
       </c>
       <c r="T7" t="n">
-        <v>4.21</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="N8" t="n">
         <v>0.93</v>
@@ -1021,7 +1021,7 @@
         <v>0.77</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6885</v>
+        <v>0.6365</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="M9" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="N9" t="n">
         <v>0.7</v>
@@ -1095,7 +1095,7 @@
         <v>0.77</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6715</v>
+        <v>0.613</v>
       </c>
       <c r="Q9" t="n">
         <v>2</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="M10" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="N10" t="n">
         <v>0.41</v>
@@ -1169,7 +1169,7 @@
         <v>0.7</v>
       </c>
       <c r="P10" t="n">
-        <v>0.629</v>
+        <v>0.5675</v>
       </c>
       <c r="Q10" t="n">
         <v>3</v>
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.64</v>
+        <v>0.88</v>
       </c>
       <c r="M11" t="n">
-        <v>0.64</v>
+        <v>0.88</v>
       </c>
       <c r="N11" t="n">
         <v>0.51</v>
@@ -1243,19 +1243,19 @@
         <v>0.6</v>
       </c>
       <c r="P11" t="n">
-        <v>0.608</v>
+        <v>0.764</v>
       </c>
       <c r="Q11" t="n">
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>8.23</v>
+        <v>2.97</v>
       </c>
       <c r="S11" t="n">
-        <v>1.56</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>8.390000000000001</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="12">
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.58</v>
+        <v>0.83</v>
       </c>
       <c r="M12" t="n">
-        <v>0.59</v>
+        <v>0.83</v>
       </c>
       <c r="N12" t="n">
         <v>0.78</v>
@@ -1317,19 +1317,19 @@
         <v>0.6</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.7855</v>
       </c>
       <c r="Q12" t="n">
         <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>9.02</v>
+        <v>3.76</v>
       </c>
       <c r="S12" t="n">
-        <v>1.71</v>
+        <v>0.71</v>
       </c>
       <c r="T12" t="n">
-        <v>9.19</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="13">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.52</v>
+        <v>0.78</v>
       </c>
       <c r="M13" t="n">
-        <v>0.53</v>
+        <v>0.78</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
@@ -1391,19 +1391,19 @@
         <v>0.6</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6315</v>
+        <v>0.797</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>9.81</v>
+        <v>4.55</v>
       </c>
       <c r="S13" t="n">
-        <v>1.86</v>
+        <v>0.86</v>
       </c>
       <c r="T13" t="n">
-        <v>10</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="14">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>0.79</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N14" t="n">
         <v>0.86</v>
@@ -1465,10 +1465,10 @@
         <v>0.75</v>
       </c>
       <c r="P14" t="n">
-        <v>0.801</v>
+        <v>0.733</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>5.88</v>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="N15" t="n">
         <v>0.93</v>
@@ -1539,7 +1539,7 @@
         <v>0.78</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8325</v>
+        <v>0.7645</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
       <c r="M16" t="n">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="N16" t="n">
         <v>0.7</v>
@@ -1613,10 +1613,10 @@
         <v>0.78</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8025</v>
+        <v>0.7315</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
         <v>5.27</v>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.76</v>
+        <v>0.65</v>
       </c>
       <c r="M17" t="n">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
       <c r="N17" t="n">
         <v>0.86</v>
@@ -1687,7 +1687,7 @@
         <v>0.73</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7755</v>
+        <v>0.7075</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="M18" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="N18" t="n">
         <v>0.61</v>
@@ -1761,7 +1761,7 @@
         <v>0.73</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7415</v>
+        <v>0.6735</v>
       </c>
       <c r="Q18" t="n">
         <v>2</v>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="N19" t="n">
         <v>0.29</v>
@@ -1835,7 +1835,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6715</v>
+        <v>0.6035</v>
       </c>
       <c r="Q19" t="n">
         <v>3</v>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="M20" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="N20" t="n">
         <v>0.41</v>
@@ -1909,19 +1909,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>0.673</v>
+        <v>0.7315</v>
       </c>
       <c r="Q20" t="n">
         <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>6.18</v>
+        <v>3.03</v>
       </c>
       <c r="S20" t="n">
-        <v>1.17</v>
+        <v>0.58</v>
       </c>
       <c r="T20" t="n">
-        <v>6.3</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="21">
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="M21" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="N21" t="n">
         <v>0.7</v>
@@ -1983,19 +1983,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>0.705</v>
+        <v>0.7635</v>
       </c>
       <c r="Q21" t="n">
         <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>6.82</v>
+        <v>3.66</v>
       </c>
       <c r="S21" t="n">
-        <v>1.29</v>
+        <v>0.7</v>
       </c>
       <c r="T21" t="n">
-        <v>6.95</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="22">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="N22" t="n">
         <v>0.93</v>
@@ -2057,19 +2057,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7185</v>
+        <v>0.787</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>7.45</v>
+        <v>4.29</v>
       </c>
       <c r="S22" t="n">
-        <v>1.41</v>
+        <v>0.82</v>
       </c>
       <c r="T22" t="n">
-        <v>7.59</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="23">
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
       <c r="M23" t="n">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
       <c r="N23" t="n">
         <v>1</v>
@@ -2131,7 +2131,7 @@
         <v>0.8</v>
       </c>
       <c r="P23" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.749</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="M24" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="N24" t="n">
         <v>0.78</v>
@@ -2205,7 +2205,7 @@
         <v>0.8</v>
       </c>
       <c r="P24" t="n">
-        <v>0.786</v>
+        <v>0.718</v>
       </c>
       <c r="Q24" t="n">
         <v>2</v>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="N25" t="n">
         <v>0.51</v>
@@ -2279,7 +2279,7 @@
         <v>0.83</v>
       </c>
       <c r="P25" t="n">
-        <v>0.753</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>3</v>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
         <v>0.7</v>
@@ -2353,19 +2353,19 @@
         <v>0.62</v>
       </c>
       <c r="P26" t="n">
-        <v>0.8245</v>
+        <v>0.883</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
         <v>0.93</v>
@@ -2427,19 +2427,19 @@
         <v>0.62</v>
       </c>
       <c r="P27" t="n">
-        <v>0.8475</v>
+        <v>0.929</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>4.85</v>
+        <v>0.48</v>
       </c>
       <c r="S27" t="n">
-        <v>0.92</v>
+        <v>0.09</v>
       </c>
       <c r="T27" t="n">
-        <v>4.94</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="28">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
         <v>0.86</v>
@@ -2501,19 +2501,19 @@
         <v>0.62</v>
       </c>
       <c r="P28" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.915</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>5.36</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T28" t="n">
         <v>1.02</v>
-      </c>
-      <c r="T28" t="n">
-        <v>5.47</v>
       </c>
     </row>
     <row r="29">
@@ -2581,13 +2581,13 @@
         <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2655,13 +2655,13 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2729,13 +2729,13 @@
         <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>2.72</v>
+        <v>0.22</v>
       </c>
       <c r="S31" t="n">
-        <v>0.52</v>
+        <v>0.04</v>
       </c>
       <c r="T31" t="n">
-        <v>2.77</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="32">
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
@@ -2797,7 +2797,7 @@
         <v>0.91</v>
       </c>
       <c r="P32" t="n">
-        <v>0.9275</v>
+        <v>0.85</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>0.92</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N33" t="n">
         <v>0.78</v>
@@ -2871,7 +2871,7 @@
         <v>0.91</v>
       </c>
       <c r="P33" t="n">
-        <v>0.8935</v>
+        <v>0.819</v>
       </c>
       <c r="Q33" t="n">
         <v>2</v>
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.95</v>
+        <v>0.82</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="N34" t="n">
         <v>0.51</v>
@@ -2945,7 +2945,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="P34" t="n">
-        <v>0.857</v>
+        <v>0.776</v>
       </c>
       <c r="Q34" t="n">
         <v>3</v>
@@ -3007,10 +3007,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
         <v>0.61</v>
@@ -3019,19 +3019,19 @@
         <v>0.71</v>
       </c>
       <c r="P35" t="n">
-        <v>0.849</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="Q35" t="n">
         <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>3.67</v>
+        <v>0.55</v>
       </c>
       <c r="S35" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="T35" t="n">
-        <v>3.82</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="36">
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
         <v>0.86</v>
@@ -3093,19 +3093,19 @@
         <v>0.71</v>
       </c>
       <c r="P36" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.9285</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
-        <v>4.05</v>
+        <v>0.92</v>
       </c>
       <c r="S36" t="n">
-        <v>0.77</v>
+        <v>0.18</v>
       </c>
       <c r="T36" t="n">
-        <v>4.21</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="37">
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="M37" t="n">
-        <v>0.89</v>
+        <v>0.98</v>
       </c>
       <c r="N37" t="n">
         <v>0.93</v>
@@ -3167,19 +3167,19 @@
         <v>0.71</v>
       </c>
       <c r="P37" t="n">
-        <v>0.877</v>
+        <v>0.9295</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>4.42</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>0.84</v>
+        <v>0.25</v>
       </c>
       <c r="T37" t="n">
-        <v>4.61</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="38">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>0.92</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N38" t="n">
         <v>1</v>
@@ -3241,7 +3241,7 @@
         <v>0.95</v>
       </c>
       <c r="P38" t="n">
-        <v>0.9465</v>
+        <v>0.869</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0.95</v>
+        <v>0.83</v>
       </c>
       <c r="M39" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="N39" t="n">
         <v>0.73</v>
@@ -3315,7 +3315,7 @@
         <v>0.95</v>
       </c>
       <c r="P39" t="n">
-        <v>0.9025</v>
+        <v>0.8245</v>
       </c>
       <c r="Q39" t="n">
         <v>2</v>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
       <c r="M40" t="n">
-        <v>0.95</v>
+        <v>0.84</v>
       </c>
       <c r="N40" t="n">
         <v>0.38</v>
@@ -3389,7 +3389,7 @@
         <v>0.95</v>
       </c>
       <c r="P40" t="n">
-        <v>0.842</v>
+        <v>0.7645</v>
       </c>
       <c r="Q40" t="n">
         <v>3</v>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="M41" t="n">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="N41" t="n">
         <v>0.78</v>
@@ -3463,7 +3463,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="P41" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.7975</v>
       </c>
       <c r="Q41" t="n">
         <v>3</v>
@@ -3525,10 +3525,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="M42" t="n">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="N42" t="n">
         <v>1</v>
@@ -3537,7 +3537,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="P42" t="n">
-        <v>0.929</v>
+        <v>0.8515</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="M43" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="N43" t="n">
         <v>0.78</v>
@@ -3611,7 +3611,7 @@
         <v>0.98</v>
       </c>
       <c r="P43" t="n">
-        <v>0.901</v>
+        <v>0.823</v>
       </c>
       <c r="Q43" t="n">
         <v>2</v>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="M44" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="N44" t="n">
         <v>0.86</v>
@@ -3685,7 +3685,7 @@
         <v>0.92</v>
       </c>
       <c r="P44" t="n">
-        <v>0.82</v>
+        <v>0.752</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="M45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="N45" t="n">
         <v>0.61</v>
@@ -3759,7 +3759,7 @@
         <v>0.92</v>
       </c>
       <c r="P45" t="n">
-        <v>0.7895</v>
+        <v>0.7215</v>
       </c>
       <c r="Q45" t="n">
         <v>2</v>
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="M46" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="N46" t="n">
         <v>0.29</v>
@@ -3833,7 +3833,7 @@
         <v>0.72</v>
       </c>
       <c r="P46" t="n">
-        <v>0.715</v>
+        <v>0.6435</v>
       </c>
       <c r="Q46" t="n">
         <v>3</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0.53</v>
+        <v>0.7</v>
       </c>
       <c r="M47" t="n">
-        <v>0.52</v>
+        <v>0.7</v>
       </c>
       <c r="N47" t="n">
         <v>0.51</v>
@@ -3907,19 +3907,19 @@
         <v>0.72</v>
       </c>
       <c r="P47" t="n">
-        <v>0.551</v>
+        <v>0.665</v>
       </c>
       <c r="Q47" t="n">
         <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>9.800000000000001</v>
+        <v>5.75</v>
       </c>
       <c r="S47" t="n">
-        <v>1.86</v>
+        <v>1.09</v>
       </c>
       <c r="T47" t="n">
-        <v>10.2</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="48">
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0.47</v>
+        <v>0.65</v>
       </c>
       <c r="M48" t="n">
-        <v>0.46</v>
+        <v>0.65</v>
       </c>
       <c r="N48" t="n">
         <v>0.78</v>
@@ -3981,19 +3981,19 @@
         <v>0.72</v>
       </c>
       <c r="P48" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.6865</v>
       </c>
       <c r="Q48" t="n">
         <v>2</v>
       </c>
       <c r="R48" t="n">
-        <v>10.61</v>
+        <v>6.56</v>
       </c>
       <c r="S48" t="n">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="T48" t="n">
-        <v>11.04</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="49">
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0.41</v>
+        <v>0.6</v>
       </c>
       <c r="M49" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="N49" t="n">
         <v>1</v>
@@ -4055,19 +4055,19 @@
         <v>0.72</v>
       </c>
       <c r="P49" t="n">
-        <v>0.571</v>
+        <v>0.698</v>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>11.42</v>
+        <v>7.37</v>
       </c>
       <c r="S49" t="n">
-        <v>2.17</v>
+        <v>1.4</v>
       </c>
       <c r="T49" t="n">
-        <v>11.89</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="50">
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
       <c r="M50" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="N50" t="n">
         <v>0.93</v>
@@ -4129,7 +4129,7 @@
         <v>0.92</v>
       </c>
       <c r="P50" t="n">
-        <v>0.873</v>
+        <v>0.7985</v>
       </c>
       <c r="Q50" t="n">
         <v>2</v>
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="M51" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="N51" t="n">
         <v>0.86</v>
@@ -4203,7 +4203,7 @@
         <v>0.92</v>
       </c>
       <c r="P51" t="n">
-        <v>0.875</v>
+        <v>0.8005</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="M52" t="n">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="N52" t="n">
         <v>0.61</v>
@@ -4277,7 +4277,7 @@
         <v>0.92</v>
       </c>
       <c r="P52" t="n">
-        <v>0.8415</v>
+        <v>0.767</v>
       </c>
       <c r="Q52" t="n">
         <v>3</v>
@@ -4339,10 +4339,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="M53" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="N53" t="n">
         <v>0.83</v>
@@ -4351,7 +4351,7 @@
         <v>0.86</v>
       </c>
       <c r="P53" t="n">
-        <v>0.857</v>
+        <v>0.7825</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="M54" t="n">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="N54" t="n">
         <v>0.51</v>
@@ -4425,7 +4425,7 @@
         <v>0.86</v>
       </c>
       <c r="P54" t="n">
-        <v>0.806</v>
+        <v>0.7315</v>
       </c>
       <c r="Q54" t="n">
         <v>2</v>
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="M55" t="n">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="N55" t="n">
         <v>0.06</v>
@@ -4499,7 +4499,7 @@
         <v>0.67</v>
       </c>
       <c r="P55" t="n">
-        <v>0.7005</v>
+        <v>0.626</v>
       </c>
       <c r="Q55" t="n">
         <v>3</v>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="M56" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N56" t="n">
         <v>0.51</v>
@@ -4573,7 +4573,7 @@
         <v>0.85</v>
       </c>
       <c r="P56" t="n">
-        <v>0.652</v>
+        <v>0.5905</v>
       </c>
       <c r="Q56" t="n">
         <v>3</v>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="M57" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="N57" t="n">
         <v>0.92</v>
@@ -4647,7 +4647,7 @@
         <v>0.85</v>
       </c>
       <c r="P57" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.695</v>
       </c>
       <c r="Q57" t="n">
         <v>1</v>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
       <c r="M58" t="n">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
       <c r="N58" t="n">
         <v>0.73</v>
@@ -4721,7 +4721,7 @@
         <v>0.85</v>
       </c>
       <c r="P58" t="n">
-        <v>0.7415</v>
+        <v>0.6765</v>
       </c>
       <c r="Q58" t="n">
         <v>2</v>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
       <c r="M59" t="n">
-        <v>0.53</v>
+        <v>0.45</v>
       </c>
       <c r="N59" t="n">
         <v>0.92</v>
@@ -4795,7 +4795,7 @@
         <v>0.84</v>
       </c>
       <c r="P59" t="n">
-        <v>0.6575</v>
+        <v>0.6055</v>
       </c>
       <c r="Q59" t="n">
         <v>2</v>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0.57</v>
+        <v>0.49</v>
       </c>
       <c r="M60" t="n">
-        <v>0.57</v>
+        <v>0.49</v>
       </c>
       <c r="N60" t="n">
         <v>0.83</v>
@@ -4869,7 +4869,7 @@
         <v>0.84</v>
       </c>
       <c r="P60" t="n">
-        <v>0.6625</v>
+        <v>0.6105</v>
       </c>
       <c r="Q60" t="n">
         <v>1</v>
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="M61" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="N61" t="n">
         <v>0.51</v>
@@ -4943,7 +4943,7 @@
         <v>0.84</v>
       </c>
       <c r="P61" t="n">
-        <v>0.621</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="Q61" t="n">
         <v>3</v>
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0.48</v>
+        <v>0.78</v>
       </c>
       <c r="M62" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="N62" t="n">
         <v>0.51</v>
@@ -5017,19 +5017,19 @@
         <v>0.66</v>
       </c>
       <c r="P62" t="n">
-        <v>0.513</v>
+        <v>0.7045</v>
       </c>
       <c r="Q62" t="n">
         <v>3</v>
       </c>
       <c r="R62" t="n">
-        <v>10.38</v>
+        <v>4.56</v>
       </c>
       <c r="S62" t="n">
-        <v>1.97</v>
+        <v>0.87</v>
       </c>
       <c r="T62" t="n">
-        <v>10.8</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="63">
@@ -5079,10 +5079,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.42</v>
+        <v>0.72</v>
       </c>
       <c r="M63" t="n">
-        <v>0.42</v>
+        <v>0.72</v>
       </c>
       <c r="N63" t="n">
         <v>0.83</v>
@@ -5091,19 +5091,19 @@
         <v>0.66</v>
       </c>
       <c r="P63" t="n">
-        <v>0.538</v>
+        <v>0.733</v>
       </c>
       <c r="Q63" t="n">
         <v>1</v>
       </c>
       <c r="R63" t="n">
-        <v>11.25</v>
+        <v>5.44</v>
       </c>
       <c r="S63" t="n">
-        <v>2.14</v>
+        <v>1.03</v>
       </c>
       <c r="T63" t="n">
-        <v>11.71</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="64">
@@ -5153,10 +5153,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0.36</v>
+        <v>0.67</v>
       </c>
       <c r="M64" t="n">
-        <v>0.35</v>
+        <v>0.66</v>
       </c>
       <c r="N64" t="n">
         <v>0.92</v>
@@ -5165,19 +5165,19 @@
         <v>0.66</v>
       </c>
       <c r="P64" t="n">
-        <v>0.5135</v>
+        <v>0.715</v>
       </c>
       <c r="Q64" t="n">
         <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>12.13</v>
+        <v>6.31</v>
       </c>
       <c r="S64" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="T64" t="n">
-        <v>12.62</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="65">
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.44</v>
+        <v>0.68</v>
       </c>
       <c r="M65" t="n">
-        <v>0.45</v>
+        <v>0.68</v>
       </c>
       <c r="N65" t="n">
         <v>0.51</v>
@@ -5239,19 +5239,19 @@
         <v>0.64</v>
       </c>
       <c r="P65" t="n">
-        <v>0.4875</v>
+        <v>0.64</v>
       </c>
       <c r="Q65" t="n">
         <v>3</v>
       </c>
       <c r="R65" t="n">
-        <v>10.95</v>
+        <v>6.15</v>
       </c>
       <c r="S65" t="n">
-        <v>2.08</v>
+        <v>1.17</v>
       </c>
       <c r="T65" t="n">
-        <v>11.16</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="66">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0.38</v>
+        <v>0.62</v>
       </c>
       <c r="M66" t="n">
-        <v>0.39</v>
+        <v>0.62</v>
       </c>
       <c r="N66" t="n">
         <v>0.78</v>
@@ -5313,19 +5313,19 @@
         <v>0.64</v>
       </c>
       <c r="P66" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.655</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R66" t="n">
-        <v>11.91</v>
+        <v>7.11</v>
       </c>
       <c r="S66" t="n">
-        <v>2.26</v>
+        <v>1.35</v>
       </c>
       <c r="T66" t="n">
-        <v>12.14</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="67">
@@ -5375,10 +5375,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.28</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M67" t="n">
-        <v>0.32</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N67" t="n">
         <v>1</v>
@@ -5387,19 +5387,19 @@
         <v>0.64</v>
       </c>
       <c r="P67" t="n">
-        <v>0.492</v>
+        <v>0.66</v>
       </c>
       <c r="Q67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>12.87</v>
+        <v>8.07</v>
       </c>
       <c r="S67" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="T67" t="n">
-        <v>13.12</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="68">
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.58</v>
+        <v>0.49</v>
       </c>
       <c r="M68" t="n">
-        <v>0.58</v>
+        <v>0.5</v>
       </c>
       <c r="N68" t="n">
         <v>0.92</v>
@@ -5461,7 +5461,7 @@
         <v>0.82</v>
       </c>
       <c r="P68" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.629</v>
       </c>
       <c r="Q68" t="n">
         <v>2</v>
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="M69" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="N69" t="n">
         <v>0.83</v>
@@ -5535,7 +5535,7 @@
         <v>0.85</v>
       </c>
       <c r="P69" t="n">
-        <v>0.6965</v>
+        <v>0.6415</v>
       </c>
       <c r="Q69" t="n">
         <v>1</v>
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="M70" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="N70" t="n">
         <v>0.51</v>
@@ -5609,7 +5609,7 @@
         <v>0.85</v>
       </c>
       <c r="P70" t="n">
-        <v>0.662</v>
+        <v>0.6035</v>
       </c>
       <c r="Q70" t="n">
         <v>3</v>
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.53</v>
+        <v>0.82</v>
       </c>
       <c r="M71" t="n">
-        <v>0.54</v>
+        <v>0.82</v>
       </c>
       <c r="N71" t="n">
         <v>0.46</v>
@@ -5683,19 +5683,19 @@
         <v>0.63</v>
       </c>
       <c r="P71" t="n">
-        <v>0.5345</v>
+        <v>0.7195</v>
       </c>
       <c r="Q71" t="n">
         <v>3</v>
       </c>
       <c r="R71" t="n">
-        <v>9.710000000000001</v>
+        <v>3.86</v>
       </c>
       <c r="S71" t="n">
-        <v>1.85</v>
+        <v>0.73</v>
       </c>
       <c r="T71" t="n">
-        <v>9.9</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="72">
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.47</v>
+        <v>0.76</v>
       </c>
       <c r="M72" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="N72" t="n">
         <v>0.8100000000000001</v>
@@ -5757,19 +5757,19 @@
         <v>0.63</v>
       </c>
       <c r="P72" t="n">
-        <v>0.5655</v>
+        <v>0.754</v>
       </c>
       <c r="Q72" t="n">
         <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>10.59</v>
+        <v>4.74</v>
       </c>
       <c r="S72" t="n">
-        <v>2.01</v>
+        <v>0.9</v>
       </c>
       <c r="T72" t="n">
-        <v>10.8</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="73">
@@ -5819,10 +5819,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.41</v>
+        <v>0.71</v>
       </c>
       <c r="M73" t="n">
-        <v>0.42</v>
+        <v>0.71</v>
       </c>
       <c r="N73" t="n">
         <v>0.91</v>
@@ -5831,19 +5831,19 @@
         <v>0.63</v>
       </c>
       <c r="P73" t="n">
-        <v>0.5465</v>
+        <v>0.738</v>
       </c>
       <c r="Q73" t="n">
         <v>2</v>
       </c>
       <c r="R73" t="n">
-        <v>11.47</v>
+        <v>5.62</v>
       </c>
       <c r="S73" t="n">
-        <v>2.18</v>
+        <v>1.07</v>
       </c>
       <c r="T73" t="n">
-        <v>11.7</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="74">
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="M74" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="N74" t="n">
         <v>0.86</v>
@@ -5905,7 +5905,7 @@
         <v>0.79</v>
       </c>
       <c r="P74" t="n">
-        <v>0.6805</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
@@ -5967,10 +5967,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M75" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="N75" t="n">
         <v>0.61</v>
@@ -5979,7 +5979,7 @@
         <v>0.82</v>
       </c>
       <c r="P75" t="n">
-        <v>0.6675</v>
+        <v>0.6125</v>
       </c>
       <c r="Q75" t="n">
         <v>2</v>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M76" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="N76" t="n">
         <v>0.29</v>
@@ -6053,7 +6053,7 @@
         <v>0.61</v>
       </c>
       <c r="P76" t="n">
-        <v>0.6045</v>
+        <v>0.543</v>
       </c>
       <c r="Q76" t="n">
         <v>3</v>
@@ -6115,10 +6115,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0.25</v>
+        <v>0.58</v>
       </c>
       <c r="M77" t="n">
-        <v>0.32</v>
+        <v>0.59</v>
       </c>
       <c r="N77" t="n">
         <v>0.51</v>
@@ -6127,19 +6127,19 @@
         <v>0.61</v>
       </c>
       <c r="P77" t="n">
-        <v>0.3805</v>
+        <v>0.574</v>
       </c>
       <c r="Q77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R77" t="n">
-        <v>12.96</v>
+        <v>7.68</v>
       </c>
       <c r="S77" t="n">
-        <v>2.46</v>
+        <v>1.46</v>
       </c>
       <c r="T77" t="n">
-        <v>13.21</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="78">
@@ -6189,10 +6189,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0.14</v>
+        <v>0.51</v>
       </c>
       <c r="M78" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="N78" t="n">
         <v>0.78</v>
@@ -6201,19 +6201,19 @@
         <v>0.61</v>
       </c>
       <c r="P78" t="n">
-        <v>0.3735</v>
+        <v>0.5825</v>
       </c>
       <c r="Q78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>14.11</v>
+        <v>8.83</v>
       </c>
       <c r="S78" t="n">
-        <v>2.68</v>
+        <v>1.68</v>
       </c>
       <c r="T78" t="n">
-        <v>14.38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
@@ -6263,10 +6263,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.06</v>
+        <v>0.44</v>
       </c>
       <c r="M79" t="n">
-        <v>0.16</v>
+        <v>0.45</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
@@ -6275,19 +6275,19 @@
         <v>0.61</v>
       </c>
       <c r="P79" t="n">
-        <v>0.3655</v>
+        <v>0.581</v>
       </c>
       <c r="Q79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R79" t="n">
-        <v>15.26</v>
+        <v>9.98</v>
       </c>
       <c r="S79" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="T79" t="n">
-        <v>15.55</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="80">
@@ -6337,10 +6337,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="M80" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="N80" t="n">
         <v>1</v>
@@ -6349,7 +6349,7 @@
         <v>0.79</v>
       </c>
       <c r="P80" t="n">
-        <v>0.543</v>
+        <v>0.5075</v>
       </c>
       <c r="Q80" t="n">
         <v>1</v>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M81" t="n">
-        <v>0.41</v>
+        <v>0.35</v>
       </c>
       <c r="N81" t="n">
         <v>0.78</v>
@@ -6423,7 +6423,7 @@
         <v>0.79</v>
       </c>
       <c r="P81" t="n">
-        <v>0.538</v>
+        <v>0.496</v>
       </c>
       <c r="Q81" t="n">
         <v>2</v>
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="M82" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="N82" t="n">
         <v>0.51</v>
@@ -6497,7 +6497,7 @@
         <v>0.82</v>
       </c>
       <c r="P82" t="n">
-        <v>0.5275</v>
+        <v>0.482</v>
       </c>
       <c r="Q82" t="n">
         <v>3</v>
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.13</v>
+        <v>0.57</v>
       </c>
       <c r="M83" t="n">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="N83" t="n">
         <v>0.61</v>
@@ -6571,19 +6571,19 @@
         <v>0.61</v>
       </c>
       <c r="P83" t="n">
-        <v>0.305</v>
+        <v>0.5875</v>
       </c>
       <c r="Q83" t="n">
         <v>1</v>
       </c>
       <c r="R83" t="n">
-        <v>15.32</v>
+        <v>7.8</v>
       </c>
       <c r="S83" t="n">
-        <v>2.91</v>
+        <v>1.48</v>
       </c>
       <c r="T83" t="n">
-        <v>15.61</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="84">
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0.04</v>
+        <v>0.49</v>
       </c>
       <c r="M84" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="N84" t="n">
         <v>0.86</v>
@@ -6645,19 +6645,19 @@
         <v>0.61</v>
       </c>
       <c r="P84" t="n">
-        <v>0.3</v>
+        <v>0.5855</v>
       </c>
       <c r="Q84" t="n">
         <v>2</v>
       </c>
       <c r="R84" t="n">
-        <v>16.61</v>
+        <v>9.09</v>
       </c>
       <c r="S84" t="n">
-        <v>3.16</v>
+        <v>1.73</v>
       </c>
       <c r="T84" t="n">
-        <v>16.93</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="85">
@@ -6707,10 +6707,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="N85" t="n">
         <v>0.93</v>
@@ -6719,19 +6719,19 @@
         <v>0.61</v>
       </c>
       <c r="P85" t="n">
-        <v>0.2775</v>
+        <v>0.5475</v>
       </c>
       <c r="Q85" t="n">
         <v>3</v>
       </c>
       <c r="R85" t="n">
-        <v>17.9</v>
+        <v>10.38</v>
       </c>
       <c r="S85" t="n">
-        <v>3.4</v>
+        <v>1.97</v>
       </c>
       <c r="T85" t="n">
-        <v>18.25</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="86">
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="M86" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="N86" t="n">
         <v>0.83</v>
@@ -6793,7 +6793,7 @@
         <v>0.78</v>
       </c>
       <c r="P86" t="n">
-        <v>0.618</v>
+        <v>0.5725</v>
       </c>
       <c r="Q86" t="n">
         <v>3</v>
@@ -6855,10 +6855,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="M87" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="N87" t="n">
         <v>0.92</v>
@@ -6867,7 +6867,7 @@
         <v>0.78</v>
       </c>
       <c r="P87" t="n">
-        <v>0.662</v>
+        <v>0.61</v>
       </c>
       <c r="Q87" t="n">
         <v>1</v>
@@ -6929,10 +6929,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="M88" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="N88" t="n">
         <v>0.63</v>
@@ -6941,7 +6941,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="P88" t="n">
-        <v>0.6345</v>
+        <v>0.5825</v>
       </c>
       <c r="Q88" t="n">
         <v>2</v>
@@ -7003,10 +7003,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0.34</v>
+        <v>0.68</v>
       </c>
       <c r="M89" t="n">
-        <v>0.44</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N89" t="n">
         <v>0.61</v>
@@ -7015,19 +7015,19 @@
         <v>0.6</v>
       </c>
       <c r="P89" t="n">
-        <v>0.468</v>
+        <v>0.6575</v>
       </c>
       <c r="Q89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R89" t="n">
-        <v>11.13</v>
+        <v>6.03</v>
       </c>
       <c r="S89" t="n">
-        <v>2.11</v>
+        <v>1.15</v>
       </c>
       <c r="T89" t="n">
-        <v>11.34</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="90">
@@ -7077,10 +7077,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.23</v>
+        <v>0.63</v>
       </c>
       <c r="M90" t="n">
-        <v>0.38</v>
+        <v>0.64</v>
       </c>
       <c r="N90" t="n">
         <v>0.86</v>
@@ -7089,19 +7089,19 @@
         <v>0.6</v>
       </c>
       <c r="P90" t="n">
-        <v>0.464</v>
+        <v>0.675</v>
       </c>
       <c r="Q90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R90" t="n">
-        <v>11.99</v>
+        <v>6.9</v>
       </c>
       <c r="S90" t="n">
-        <v>2.28</v>
+        <v>1.31</v>
       </c>
       <c r="T90" t="n">
-        <v>12.23</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="91">
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.14</v>
+        <v>0.57</v>
       </c>
       <c r="M91" t="n">
-        <v>0.32</v>
+        <v>0.58</v>
       </c>
       <c r="N91" t="n">
         <v>0.93</v>
@@ -7163,19 +7163,19 @@
         <v>0.6</v>
       </c>
       <c r="P91" t="n">
-        <v>0.43</v>
+        <v>0.65</v>
       </c>
       <c r="Q91" t="n">
         <v>3</v>
       </c>
       <c r="R91" t="n">
-        <v>12.86</v>
+        <v>7.77</v>
       </c>
       <c r="S91" t="n">
-        <v>2.44</v>
+        <v>1.48</v>
       </c>
       <c r="T91" t="n">
-        <v>13.11</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="92">
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0.42</v>
+        <v>0.71</v>
       </c>
       <c r="M92" t="n">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="N92" t="n">
         <v>0.61</v>
@@ -7237,19 +7237,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="P92" t="n">
-        <v>0.4965</v>
+        <v>0.6745</v>
       </c>
       <c r="Q92" t="n">
         <v>2</v>
       </c>
       <c r="R92" t="n">
-        <v>11.22</v>
+        <v>5.63</v>
       </c>
       <c r="S92" t="n">
-        <v>2.13</v>
+        <v>1.07</v>
       </c>
       <c r="T92" t="n">
-        <v>10.95</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="93">
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.36</v>
+        <v>0.65</v>
       </c>
       <c r="M93" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="N93" t="n">
         <v>0.86</v>
@@ -7311,19 +7311,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="P93" t="n">
-        <v>0.504</v>
+        <v>0.6855</v>
       </c>
       <c r="Q93" t="n">
         <v>1</v>
       </c>
       <c r="R93" t="n">
-        <v>12.18</v>
+        <v>6.59</v>
       </c>
       <c r="S93" t="n">
-        <v>2.31</v>
+        <v>1.25</v>
       </c>
       <c r="T93" t="n">
-        <v>11.89</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="94">
@@ -7373,10 +7373,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.29</v>
+        <v>0.59</v>
       </c>
       <c r="M94" t="n">
-        <v>0.34</v>
+        <v>0.62</v>
       </c>
       <c r="N94" t="n">
         <v>0.93</v>
@@ -7385,19 +7385,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="P94" t="n">
-        <v>0.476</v>
+        <v>0.664</v>
       </c>
       <c r="Q94" t="n">
         <v>3</v>
       </c>
       <c r="R94" t="n">
-        <v>13.14</v>
+        <v>7.55</v>
       </c>
       <c r="S94" t="n">
-        <v>2.5</v>
+        <v>1.43</v>
       </c>
       <c r="T94" t="n">
-        <v>12.83</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="95">
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="M98" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="N98" t="n">
         <v>1</v>
@@ -7681,7 +7681,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="P98" t="n">
-        <v>0.6465</v>
+        <v>0.598</v>
       </c>
       <c r="Q98" t="n">
         <v>1</v>
@@ -7743,10 +7743,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="M99" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="N99" t="n">
         <v>0.86</v>
@@ -7755,7 +7755,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="P99" t="n">
-        <v>0.635</v>
+        <v>0.5865</v>
       </c>
       <c r="Q99" t="n">
         <v>2</v>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="M100" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="N100" t="n">
         <v>0.7</v>
@@ -7829,7 +7829,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="P100" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.5705</v>
       </c>
       <c r="Q100" t="n">
         <v>3</v>
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
         <v>0.02</v>
-      </c>
-      <c r="M103" t="n">
-        <v>0.04</v>
       </c>
       <c r="N103" t="n">
         <v>0.23</v>
@@ -8051,7 +8051,7 @@
         <v>0.67</v>
       </c>
       <c r="P103" t="n">
-        <v>0.1665</v>
+        <v>0.1535</v>
       </c>
       <c r="Q103" t="n">
         <v>3</v>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="M104" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="N104" t="n">
         <v>0.93</v>
@@ -8125,7 +8125,7 @@
         <v>0.82</v>
       </c>
       <c r="P104" t="n">
-        <v>0.7215</v>
+        <v>0.6665</v>
       </c>
       <c r="Q104" t="n">
         <v>1</v>
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M105" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="N105" t="n">
         <v>0.78</v>
@@ -8199,7 +8199,7 @@
         <v>0.82</v>
       </c>
       <c r="P105" t="n">
-        <v>0.711</v>
+        <v>0.6495</v>
       </c>
       <c r="Q105" t="n">
         <v>2</v>
@@ -8261,10 +8261,10 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="M106" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="N106" t="n">
         <v>0.61</v>
@@ -8273,7 +8273,7 @@
         <v>0.82</v>
       </c>
       <c r="P106" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="Q106" t="n">
         <v>3</v>
@@ -8335,10 +8335,10 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="M107" t="n">
-        <v>0.58</v>
+        <v>0.91</v>
       </c>
       <c r="N107" t="n">
         <v>0.51</v>
@@ -8347,19 +8347,19 @@
         <v>0.57</v>
       </c>
       <c r="P107" t="n">
-        <v>0.5615</v>
+        <v>0.779</v>
       </c>
       <c r="Q107" t="n">
         <v>3</v>
       </c>
       <c r="R107" t="n">
-        <v>9.15</v>
+        <v>2.5</v>
       </c>
       <c r="S107" t="n">
-        <v>1.74</v>
+        <v>0.47</v>
       </c>
       <c r="T107" t="n">
-        <v>9.33</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="108">
@@ -8409,10 +8409,10 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0.51</v>
+        <v>0.85</v>
       </c>
       <c r="M108" t="n">
-        <v>0.52</v>
+        <v>0.85</v>
       </c>
       <c r="N108" t="n">
         <v>0.78</v>
@@ -8421,19 +8421,19 @@
         <v>0.57</v>
       </c>
       <c r="P108" t="n">
-        <v>0.5765</v>
+        <v>0.794</v>
       </c>
       <c r="Q108" t="n">
         <v>2</v>
       </c>
       <c r="R108" t="n">
-        <v>9.99</v>
+        <v>3.33</v>
       </c>
       <c r="S108" t="n">
-        <v>1.9</v>
+        <v>0.63</v>
       </c>
       <c r="T108" t="n">
-        <v>10.18</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="109">
@@ -8483,10 +8483,10 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0.45</v>
+        <v>0.8</v>
       </c>
       <c r="M109" t="n">
-        <v>0.46</v>
+        <v>0.8</v>
       </c>
       <c r="N109" t="n">
         <v>1</v>
@@ -8495,19 +8495,19 @@
         <v>0.57</v>
       </c>
       <c r="P109" t="n">
-        <v>0.5815</v>
+        <v>0.8055</v>
       </c>
       <c r="Q109" t="n">
         <v>1</v>
       </c>
       <c r="R109" t="n">
-        <v>10.82</v>
+        <v>4.17</v>
       </c>
       <c r="S109" t="n">
-        <v>2.06</v>
+        <v>0.79</v>
       </c>
       <c r="T109" t="n">
-        <v>11.03</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="110">
@@ -8557,10 +8557,10 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0.59</v>
+        <v>0.5</v>
       </c>
       <c r="M110" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="N110" t="n">
         <v>1</v>
@@ -8569,7 +8569,7 @@
         <v>0.83</v>
       </c>
       <c r="P110" t="n">
-        <v>0.708</v>
+        <v>0.653</v>
       </c>
       <c r="Q110" t="n">
         <v>1</v>
@@ -8631,10 +8631,10 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="M111" t="n">
-        <v>0.61</v>
+        <v>0.53</v>
       </c>
       <c r="N111" t="n">
         <v>0.93</v>
@@ -8643,7 +8643,7 @@
         <v>0.83</v>
       </c>
       <c r="P111" t="n">
-        <v>0.704</v>
+        <v>0.652</v>
       </c>
       <c r="Q111" t="n">
         <v>2</v>
@@ -8705,10 +8705,10 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="M112" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="N112" t="n">
         <v>0.86</v>
@@ -8717,7 +8717,7 @@
         <v>0.83</v>
       </c>
       <c r="P112" t="n">
-        <v>0.6995</v>
+        <v>0.6445</v>
       </c>
       <c r="Q112" t="n">
         <v>3</v>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
       <c r="M113" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="N113" t="n">
         <v>0.45</v>
@@ -8791,7 +8791,7 @@
         <v>0.91</v>
       </c>
       <c r="P113" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="Q113" t="n">
         <v>2</v>
@@ -8853,10 +8853,10 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="M114" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="N114" t="n">
         <v>1</v>
@@ -8865,7 +8865,7 @@
         <v>0.87</v>
       </c>
       <c r="P114" t="n">
-        <v>0.756</v>
+        <v>0.701</v>
       </c>
       <c r="Q114" t="n">
         <v>1</v>
@@ -8927,10 +8927,10 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="M115" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="N115" t="n">
         <v>0.45</v>
@@ -8939,7 +8939,7 @@
         <v>0.74</v>
       </c>
       <c r="P115" t="n">
-        <v>0.5875</v>
+        <v>0.5355</v>
       </c>
       <c r="Q115" t="n">
         <v>3</v>
@@ -9001,10 +9001,10 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0.44</v>
+        <v>0.76</v>
       </c>
       <c r="M116" t="n">
-        <v>0.45</v>
+        <v>0.76</v>
       </c>
       <c r="N116" t="n">
         <v>0.51</v>
@@ -9013,19 +9013,19 @@
         <v>0.64</v>
       </c>
       <c r="P116" t="n">
-        <v>0.4875</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="Q116" t="n">
         <v>1</v>
       </c>
       <c r="R116" t="n">
-        <v>11.05</v>
+        <v>4.82</v>
       </c>
       <c r="S116" t="n">
-        <v>2.1</v>
+        <v>0.92</v>
       </c>
       <c r="T116" t="n">
-        <v>11.27</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="117">
@@ -9075,10 +9075,10 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0.28</v>
+        <v>0.62</v>
       </c>
       <c r="M117" t="n">
-        <v>0.29</v>
+        <v>0.62</v>
       </c>
       <c r="N117" t="n">
         <v>0.93</v>
@@ -9087,19 +9087,19 @@
         <v>0.64</v>
       </c>
       <c r="P117" t="n">
-        <v>0.4675</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="Q117" t="n">
         <v>2</v>
       </c>
       <c r="R117" t="n">
-        <v>13.33</v>
+        <v>7.1</v>
       </c>
       <c r="S117" t="n">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="T117" t="n">
-        <v>13.59</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="118">
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0.11</v>
+        <v>0.47</v>
       </c>
       <c r="M118" t="n">
-        <v>0.13</v>
+        <v>0.48</v>
       </c>
       <c r="N118" t="n">
         <v>0.29</v>
@@ -9161,19 +9161,19 @@
         <v>0.5</v>
       </c>
       <c r="P118" t="n">
-        <v>0.2115</v>
+        <v>0.442</v>
       </c>
       <c r="Q118" t="n">
         <v>3</v>
       </c>
       <c r="R118" t="n">
-        <v>15.61</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="S118" t="n">
-        <v>2.97</v>
+        <v>1.78</v>
       </c>
       <c r="T118" t="n">
-        <v>15.91</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="119">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="N119" t="n">
         <v>0.86</v>
@@ -9235,10 +9235,10 @@
         <v>0.72</v>
       </c>
       <c r="P119" t="n">
-        <v>0.297</v>
+        <v>0.287</v>
       </c>
       <c r="Q119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R119" t="n">
         <v>16.93</v>
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="M120" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N120" t="n">
         <v>0.7</v>
@@ -9309,10 +9309,10 @@
         <v>0.72</v>
       </c>
       <c r="P120" t="n">
-        <v>0.301</v>
+        <v>0.2815</v>
       </c>
       <c r="Q120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R120" t="n">
         <v>16.15</v>
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="M121" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="N121" t="n">
         <v>0.51</v>
@@ -9383,7 +9383,7 @@
         <v>0.72</v>
       </c>
       <c r="P121" t="n">
-        <v>0.2955</v>
+        <v>0.276</v>
       </c>
       <c r="Q121" t="n">
         <v>3</v>
@@ -9445,10 +9445,10 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0.83</v>
+        <v>0.97</v>
       </c>
       <c r="M122" t="n">
-        <v>0.84</v>
+        <v>0.97</v>
       </c>
       <c r="N122" t="n">
         <v>0.93</v>
@@ -9457,19 +9457,19 @@
         <v>0.67</v>
       </c>
       <c r="P122" t="n">
-        <v>0.8295</v>
+        <v>0.917</v>
       </c>
       <c r="Q122" t="n">
         <v>1</v>
       </c>
       <c r="R122" t="n">
-        <v>5.55</v>
+        <v>1.44</v>
       </c>
       <c r="S122" t="n">
-        <v>1.05</v>
+        <v>0.27</v>
       </c>
       <c r="T122" t="n">
-        <v>5.41</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="123">
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="N123" t="n">
         <v>0.51</v>
@@ -9531,19 +9531,19 @@
         <v>0.67</v>
       </c>
       <c r="P123" t="n">
-        <v>0.781</v>
+        <v>0.8525</v>
       </c>
       <c r="Q123" t="n">
         <v>2</v>
       </c>
       <c r="R123" t="n">
-        <v>4.72</v>
+        <v>0.61</v>
       </c>
       <c r="S123" t="n">
-        <v>0.9</v>
+        <v>0.12</v>
       </c>
       <c r="T123" t="n">
-        <v>4.6</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="124">
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="N124" t="n">
         <v>0</v>
@@ -9605,19 +9605,19 @@
         <v>0.32</v>
       </c>
       <c r="P124" t="n">
-        <v>0.6625</v>
+        <v>0.698</v>
       </c>
       <c r="Q124" t="n">
         <v>3</v>
       </c>
       <c r="R124" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="T124" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -9667,10 +9667,10 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="M125" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="N125" t="n">
         <v>0.76</v>
@@ -9679,7 +9679,7 @@
         <v>0.78</v>
       </c>
       <c r="P125" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.516</v>
       </c>
       <c r="Q125" t="n">
         <v>1</v>
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="M126" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="N126" t="n">
         <v>0.5600000000000001</v>
@@ -9753,7 +9753,7 @@
         <v>0.78</v>
       </c>
       <c r="P126" t="n">
-        <v>0.544</v>
+        <v>0.4955</v>
       </c>
       <c r="Q126" t="n">
         <v>2</v>
@@ -9815,10 +9815,10 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0.53</v>
+        <v>0.45</v>
       </c>
       <c r="M127" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="N127" t="n">
         <v>0.32</v>
@@ -9827,7 +9827,7 @@
         <v>0.68</v>
       </c>
       <c r="P127" t="n">
-        <v>0.507</v>
+        <v>0.4585</v>
       </c>
       <c r="Q127" t="n">
         <v>3</v>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0.83</v>
+        <v>0.97</v>
       </c>
       <c r="M128" t="n">
-        <v>0.84</v>
+        <v>0.97</v>
       </c>
       <c r="N128" t="n">
         <v>0.51</v>
@@ -9901,19 +9901,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="P128" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.836</v>
       </c>
       <c r="Q128" t="n">
         <v>3</v>
       </c>
       <c r="R128" t="n">
-        <v>5.49</v>
+        <v>1.54</v>
       </c>
       <c r="S128" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="T128" t="n">
-        <v>5.36</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="129">
@@ -9963,10 +9963,10 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M129" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N129" t="n">
         <v>0.78</v>
@@ -9975,19 +9975,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="P129" t="n">
-        <v>0.783</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="Q129" t="n">
         <v>2</v>
       </c>
       <c r="R129" t="n">
-        <v>5.97</v>
+        <v>2.02</v>
       </c>
       <c r="S129" t="n">
-        <v>1.13</v>
+        <v>0.38</v>
       </c>
       <c r="T129" t="n">
-        <v>5.83</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="130">
@@ -10037,10 +10037,10 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0.77</v>
+        <v>0.92</v>
       </c>
       <c r="M130" t="n">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="N130" t="n">
         <v>0.93</v>
@@ -10049,19 +10049,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="P130" t="n">
-        <v>0.797</v>
+        <v>0.8875</v>
       </c>
       <c r="Q130" t="n">
         <v>1</v>
       </c>
       <c r="R130" t="n">
-        <v>6.29</v>
+        <v>2.34</v>
       </c>
       <c r="S130" t="n">
-        <v>1.2</v>
+        <v>0.44</v>
       </c>
       <c r="T130" t="n">
-        <v>6.14</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="131">
@@ -10111,10 +10111,10 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0.59</v>
+        <v>0.5</v>
       </c>
       <c r="M131" t="n">
-        <v>0.58</v>
+        <v>0.5</v>
       </c>
       <c r="N131" t="n">
         <v>0.86</v>
@@ -10123,7 +10123,7 @@
         <v>0.78</v>
       </c>
       <c r="P131" t="n">
-        <v>0.669</v>
+        <v>0.614</v>
       </c>
       <c r="Q131" t="n">
         <v>1</v>
@@ -10185,10 +10185,10 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="M132" t="n">
-        <v>0.61</v>
+        <v>0.53</v>
       </c>
       <c r="N132" t="n">
         <v>0.7</v>
@@ -10197,7 +10197,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="P132" t="n">
-        <v>0.661</v>
+        <v>0.606</v>
       </c>
       <c r="Q132" t="n">
         <v>2</v>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M133" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="N133" t="n">
         <v>0.51</v>
@@ -10271,7 +10271,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="P133" t="n">
-        <v>0.6425</v>
+        <v>0.584</v>
       </c>
       <c r="Q133" t="n">
         <v>3</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="N134" t="n">
         <v>0</v>
@@ -10345,19 +10345,19 @@
         <v>0.29</v>
       </c>
       <c r="P134" t="n">
-        <v>0.0435</v>
+        <v>0.115</v>
       </c>
       <c r="Q134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R134" t="n">
-        <v>22.52</v>
+        <v>15.13</v>
       </c>
       <c r="S134" t="n">
-        <v>4.28</v>
+        <v>2.87</v>
       </c>
       <c r="T134" t="n">
-        <v>23.45</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="135">
@@ -10422,16 +10422,16 @@
         <v>0.1035</v>
       </c>
       <c r="Q135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R135" t="n">
-        <v>24.29</v>
+        <v>16.9</v>
       </c>
       <c r="S135" t="n">
-        <v>4.62</v>
+        <v>3.21</v>
       </c>
       <c r="T135" t="n">
-        <v>25.29</v>
+        <v>17.59</v>
       </c>
     </row>
     <row r="136">
@@ -10499,13 +10499,13 @@
         <v>1</v>
       </c>
       <c r="R136" t="n">
-        <v>26.65</v>
+        <v>19.26</v>
       </c>
       <c r="S136" t="n">
-        <v>5.06</v>
+        <v>3.66</v>
       </c>
       <c r="T136" t="n">
-        <v>27.75</v>
+        <v>20.05</v>
       </c>
     </row>
     <row r="137">
@@ -10555,10 +10555,10 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="M137" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="N137" t="n">
         <v>0.78</v>
@@ -10567,7 +10567,7 @@
         <v>0.88</v>
       </c>
       <c r="P137" t="n">
-        <v>0.7495000000000001</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="Q137" t="n">
         <v>3</v>
@@ -10629,10 +10629,10 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="M138" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="N138" t="n">
         <v>1</v>
@@ -10641,7 +10641,7 @@
         <v>0.88</v>
       </c>
       <c r="P138" t="n">
-        <v>0.8195</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="Q138" t="n">
         <v>1</v>
@@ -10703,10 +10703,10 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M139" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N139" t="n">
         <v>0.78</v>
@@ -10715,7 +10715,7 @@
         <v>0.88</v>
       </c>
       <c r="P139" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.7365</v>
       </c>
       <c r="Q139" t="n">
         <v>2</v>
@@ -10777,10 +10777,10 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0.53</v>
+        <v>0.45</v>
       </c>
       <c r="M140" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="N140" t="n">
         <v>0.83</v>
@@ -10789,7 +10789,7 @@
         <v>0.91</v>
       </c>
       <c r="P140" t="n">
-        <v>0.647</v>
+        <v>0.5985</v>
       </c>
       <c r="Q140" t="n">
         <v>3</v>
@@ -10851,10 +10851,10 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="M141" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="N141" t="n">
         <v>0.83</v>
@@ -10863,7 +10863,7 @@
         <v>0.91</v>
       </c>
       <c r="P141" t="n">
-        <v>0.6925</v>
+        <v>0.6375</v>
       </c>
       <c r="Q141" t="n">
         <v>1</v>
@@ -10925,10 +10925,10 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0.64</v>
+        <v>0.54</v>
       </c>
       <c r="M142" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="N142" t="n">
         <v>0.63</v>
@@ -10937,7 +10937,7 @@
         <v>0.91</v>
       </c>
       <c r="P142" t="n">
-        <v>0.6785</v>
+        <v>0.617</v>
       </c>
       <c r="Q142" t="n">
         <v>2</v>
@@ -10999,10 +10999,10 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="M143" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="N143" t="n">
         <v>0.78</v>
@@ -11011,7 +11011,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="P143" t="n">
-        <v>0.8655</v>
+        <v>0.791</v>
       </c>
       <c r="Q143" t="n">
         <v>3</v>
@@ -11073,10 +11073,10 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="M144" t="n">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="N144" t="n">
         <v>0.93</v>
@@ -11085,7 +11085,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="P144" t="n">
-        <v>0.912</v>
+        <v>0.8375</v>
       </c>
       <c r="Q144" t="n">
         <v>1</v>
@@ -11147,10 +11147,10 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="M145" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="N145" t="n">
         <v>0.7</v>
@@ -11159,7 +11159,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="P145" t="n">
-        <v>0.879</v>
+        <v>0.801</v>
       </c>
       <c r="Q145" t="n">
         <v>2</v>
@@ -11239,13 +11239,13 @@
         <v>3</v>
       </c>
       <c r="R146" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -11313,13 +11313,13 @@
         <v>2</v>
       </c>
       <c r="R147" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -11372,7 +11372,7 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="N148" t="n">
         <v>0.93</v>
@@ -11381,19 +11381,19 @@
         <v>0.76</v>
       </c>
       <c r="P148" t="n">
-        <v>0.9465</v>
+        <v>0.95</v>
       </c>
       <c r="Q148" t="n">
         <v>1</v>
       </c>
       <c r="R148" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S148" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -11443,10 +11443,10 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="N149" t="n">
         <v>0.51</v>
@@ -11455,19 +11455,19 @@
         <v>0.72</v>
       </c>
       <c r="P149" t="n">
-        <v>0.8305</v>
+        <v>0.86</v>
       </c>
       <c r="Q149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R149" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -11517,10 +11517,10 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="N150" t="n">
         <v>0.78</v>
@@ -11529,19 +11529,19 @@
         <v>0.72</v>
       </c>
       <c r="P150" t="n">
-        <v>0.8425</v>
+        <v>0.914</v>
       </c>
       <c r="Q150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R150" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -11591,10 +11591,10 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N151" t="n">
         <v>0.93</v>
@@ -11603,19 +11603,19 @@
         <v>0.72</v>
       </c>
       <c r="P151" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.944</v>
       </c>
       <c r="Q151" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R151" t="n">
-        <v>5.83</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="S151" t="n">
-        <v>1.11</v>
+        <v>0.01</v>
       </c>
       <c r="T151" t="n">
-        <v>5.94</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="152">
@@ -11668,7 +11668,7 @@
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="N152" t="n">
         <v>0.5600000000000001</v>
@@ -11677,19 +11677,19 @@
         <v>0.75</v>
       </c>
       <c r="P152" t="n">
-        <v>0.871</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="Q152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R152" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="T152" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -11739,10 +11739,10 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="N153" t="n">
         <v>0.93</v>
@@ -11751,19 +11751,19 @@
         <v>0.75</v>
       </c>
       <c r="P153" t="n">
-        <v>0.8995</v>
+        <v>0.9485</v>
       </c>
       <c r="Q153" t="n">
         <v>1</v>
       </c>
       <c r="R153" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="T153" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -11813,10 +11813,10 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="N154" t="n">
         <v>0.76</v>
@@ -11825,19 +11825,19 @@
         <v>0.75</v>
       </c>
       <c r="P154" t="n">
-        <v>0.82</v>
+        <v>0.9145</v>
       </c>
       <c r="Q154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R154" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="T154" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -11887,10 +11887,10 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="M155" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="N155" t="n">
         <v>0.61</v>
@@ -11899,7 +11899,7 @@
         <v>0.75</v>
       </c>
       <c r="P155" t="n">
-        <v>0.459</v>
+        <v>0.4235</v>
       </c>
       <c r="Q155" t="n">
         <v>3</v>
@@ -11961,10 +11961,10 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="M156" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="N156" t="n">
         <v>1</v>
@@ -11973,7 +11973,7 @@
         <v>0.82</v>
       </c>
       <c r="P156" t="n">
-        <v>0.5995</v>
+        <v>0.5605</v>
       </c>
       <c r="Q156" t="n">
         <v>1</v>
@@ -12035,10 +12035,10 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="M157" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="N157" t="n">
         <v>0.51</v>
@@ -12047,7 +12047,7 @@
         <v>0.82</v>
       </c>
       <c r="P157" t="n">
-        <v>0.5665</v>
+        <v>0.521</v>
       </c>
       <c r="Q157" t="n">
         <v>2</v>
@@ -12112,7 +12112,7 @@
         <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
         <v>0.45</v>
@@ -12121,7 +12121,7 @@
         <v>0.67</v>
       </c>
       <c r="P158" t="n">
-        <v>0.1975</v>
+        <v>0.1905</v>
       </c>
       <c r="Q158" t="n">
         <v>3</v>
@@ -12183,10 +12183,10 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="M159" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="N159" t="n">
         <v>1</v>
@@ -12195,7 +12195,7 @@
         <v>0.8</v>
       </c>
       <c r="P159" t="n">
-        <v>0.444</v>
+        <v>0.418</v>
       </c>
       <c r="Q159" t="n">
         <v>2</v>
@@ -12257,10 +12257,10 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="M160" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="N160" t="n">
         <v>0.76</v>
@@ -12269,7 +12269,7 @@
         <v>0.8</v>
       </c>
       <c r="P160" t="n">
-        <v>0.4575</v>
+        <v>0.422</v>
       </c>
       <c r="Q160" t="n">
         <v>1</v>
@@ -12331,10 +12331,10 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="M161" t="n">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
       <c r="N161" t="n">
         <v>0.78</v>
@@ -12343,7 +12343,7 @@
         <v>0.85</v>
       </c>
       <c r="P161" t="n">
-        <v>0.7805</v>
+        <v>0.7125</v>
       </c>
       <c r="Q161" t="n">
         <v>2</v>
@@ -12405,10 +12405,10 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M162" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="N162" t="n">
         <v>0.93</v>
@@ -12417,7 +12417,7 @@
         <v>0.85</v>
       </c>
       <c r="P162" t="n">
-        <v>0.8265</v>
+        <v>0.7585</v>
       </c>
       <c r="Q162" t="n">
         <v>1</v>
@@ -12479,10 +12479,10 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
       <c r="M163" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="N163" t="n">
         <v>0.51</v>
@@ -12491,7 +12491,7 @@
         <v>0.85</v>
       </c>
       <c r="P163" t="n">
-        <v>0.7655</v>
+        <v>0.6975</v>
       </c>
       <c r="Q163" t="n">
         <v>3</v>
@@ -12553,10 +12553,10 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0.37</v>
+        <v>0.72</v>
       </c>
       <c r="M164" t="n">
-        <v>0.38</v>
+        <v>0.72</v>
       </c>
       <c r="N164" t="n">
         <v>0.41</v>
@@ -12565,19 +12565,19 @@
         <v>0.63</v>
       </c>
       <c r="P164" t="n">
-        <v>0.4205</v>
+        <v>0.6445</v>
       </c>
       <c r="Q164" t="n">
         <v>2</v>
       </c>
       <c r="R164" t="n">
-        <v>12.02</v>
+        <v>5.48</v>
       </c>
       <c r="S164" t="n">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="T164" t="n">
-        <v>12.26</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="165">
@@ -12627,10 +12627,10 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0.26</v>
+        <v>0.63</v>
       </c>
       <c r="M165" t="n">
-        <v>0.29</v>
+        <v>0.64</v>
       </c>
       <c r="N165" t="n">
         <v>0.78</v>
@@ -12639,19 +12639,19 @@
         <v>0.63</v>
       </c>
       <c r="P165" t="n">
-        <v>0.43</v>
+        <v>0.6635</v>
       </c>
       <c r="Q165" t="n">
         <v>1</v>
       </c>
       <c r="R165" t="n">
-        <v>13.39</v>
+        <v>6.84</v>
       </c>
       <c r="S165" t="n">
-        <v>2.54</v>
+        <v>1.3</v>
       </c>
       <c r="T165" t="n">
-        <v>13.65</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="166">
@@ -12701,10 +12701,10 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0.08</v>
+        <v>0.5</v>
       </c>
       <c r="M166" t="n">
-        <v>0.15</v>
+        <v>0.51</v>
       </c>
       <c r="N166" t="n">
         <v>0.78</v>
@@ -12713,19 +12713,19 @@
         <v>0.63</v>
       </c>
       <c r="P166" t="n">
-        <v>0.327</v>
+        <v>0.579</v>
       </c>
       <c r="Q166" t="n">
         <v>3</v>
       </c>
       <c r="R166" t="n">
-        <v>15.44</v>
+        <v>8.9</v>
       </c>
       <c r="S166" t="n">
-        <v>2.93</v>
+        <v>1.69</v>
       </c>
       <c r="T166" t="n">
-        <v>15.74</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="167">
@@ -12775,10 +12775,10 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0.41</v>
+        <v>0.71</v>
       </c>
       <c r="M167" t="n">
-        <v>0.45</v>
+        <v>0.71</v>
       </c>
       <c r="N167" t="n">
         <v>0.51</v>
@@ -12787,19 +12787,19 @@
         <v>0.59</v>
       </c>
       <c r="P167" t="n">
-        <v>0.471</v>
+        <v>0.652</v>
       </c>
       <c r="Q167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R167" t="n">
-        <v>11.04</v>
+        <v>5.63</v>
       </c>
       <c r="S167" t="n">
-        <v>2.1</v>
+        <v>1.07</v>
       </c>
       <c r="T167" t="n">
-        <v>11.26</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="168">
@@ -12849,10 +12849,10 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="M168" t="n">
-        <v>0.33</v>
+        <v>0.61</v>
       </c>
       <c r="N168" t="n">
         <v>0.93</v>
@@ -12861,19 +12861,19 @@
         <v>0.59</v>
       </c>
       <c r="P168" t="n">
-        <v>0.45</v>
+        <v>0.668</v>
       </c>
       <c r="Q168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R168" t="n">
-        <v>12.7</v>
+        <v>7.29</v>
       </c>
       <c r="S168" t="n">
-        <v>2.41</v>
+        <v>1.39</v>
       </c>
       <c r="T168" t="n">
-        <v>12.94</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="169">
@@ -12923,10 +12923,10 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="M169" t="n">
-        <v>0.2</v>
+        <v>0.49</v>
       </c>
       <c r="N169" t="n">
         <v>0.61</v>
@@ -12935,19 +12935,19 @@
         <v>0.59</v>
       </c>
       <c r="P169" t="n">
-        <v>0.3015</v>
+        <v>0.526</v>
       </c>
       <c r="Q169" t="n">
         <v>3</v>
       </c>
       <c r="R169" t="n">
-        <v>14.69</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="S169" t="n">
-        <v>2.79</v>
+        <v>1.76</v>
       </c>
       <c r="T169" t="n">
-        <v>14.97</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="170">
@@ -12997,10 +12997,10 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="M170" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="N170" t="n">
         <v>0.86</v>
@@ -13009,10 +13009,10 @@
         <v>0.82</v>
       </c>
       <c r="P170" t="n">
-        <v>0.7045</v>
+        <v>0.646</v>
       </c>
       <c r="Q170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R170" t="n">
         <v>8.26</v>
@@ -13071,10 +13071,10 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="M171" t="n">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
       <c r="N171" t="n">
         <v>0.15</v>
@@ -13083,7 +13083,7 @@
         <v>0.51</v>
       </c>
       <c r="P171" t="n">
-        <v>0.5775</v>
+        <v>0.5125</v>
       </c>
       <c r="Q171" t="n">
         <v>3</v>
@@ -13160,7 +13160,7 @@
         <v>0.6725</v>
       </c>
       <c r="Q172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R172" t="n">
         <v>0</v>
@@ -13219,10 +13219,10 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="M173" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="N173" t="n">
         <v>0.86</v>
@@ -13231,7 +13231,7 @@
         <v>0.85</v>
       </c>
       <c r="P173" t="n">
-        <v>0.777</v>
+        <v>0.7155</v>
       </c>
       <c r="Q173" t="n">
         <v>1</v>
@@ -13293,10 +13293,10 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="M174" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="N174" t="n">
         <v>0.15</v>
@@ -13305,7 +13305,7 @@
         <v>0.54</v>
       </c>
       <c r="P174" t="n">
-        <v>0.634</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="Q174" t="n">
         <v>3</v>
@@ -13441,10 +13441,10 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="M176" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="N176" t="n">
         <v>0.76</v>
@@ -13453,7 +13453,7 @@
         <v>0.9</v>
       </c>
       <c r="P176" t="n">
-        <v>0.7425</v>
+        <v>0.681</v>
       </c>
       <c r="Q176" t="n">
         <v>3</v>
@@ -13515,10 +13515,10 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="M177" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="N177" t="n">
         <v>0.93</v>
@@ -13527,7 +13527,7 @@
         <v>0.93</v>
       </c>
       <c r="P177" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.742</v>
       </c>
       <c r="Q177" t="n">
         <v>1</v>
@@ -13589,10 +13589,10 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
       <c r="M178" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="N178" t="n">
         <v>0.67</v>
@@ -13601,7 +13601,7 @@
         <v>0.93</v>
       </c>
       <c r="P178" t="n">
-        <v>0.7745</v>
+        <v>0.7095</v>
       </c>
       <c r="Q178" t="n">
         <v>2</v>
@@ -13663,10 +13663,10 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
       <c r="M179" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="N179" t="n">
         <v>0.51</v>
@@ -13675,19 +13675,19 @@
         <v>0.64</v>
       </c>
       <c r="P179" t="n">
-        <v>0.6825</v>
+        <v>0.7735</v>
       </c>
       <c r="Q179" t="n">
         <v>3</v>
       </c>
       <c r="R179" t="n">
-        <v>6.84</v>
+        <v>2.95</v>
       </c>
       <c r="S179" t="n">
-        <v>1.3</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T179" t="n">
-        <v>6.68</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="180">
@@ -13737,10 +13737,10 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="M180" t="n">
-        <v>0.72</v>
+        <v>0.86</v>
       </c>
       <c r="N180" t="n">
         <v>0.78</v>
@@ -13749,19 +13749,19 @@
         <v>0.64</v>
       </c>
       <c r="P180" t="n">
-        <v>0.714</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="Q180" t="n">
         <v>2</v>
       </c>
       <c r="R180" t="n">
-        <v>7.35</v>
+        <v>3.46</v>
       </c>
       <c r="S180" t="n">
-        <v>1.4</v>
+        <v>0.66</v>
       </c>
       <c r="T180" t="n">
-        <v>7.18</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="181">
@@ -13811,10 +13811,10 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="M181" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="N181" t="n">
         <v>0.93</v>
@@ -13823,19 +13823,19 @@
         <v>0.64</v>
       </c>
       <c r="P181" t="n">
-        <v>0.715</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="Q181" t="n">
         <v>1</v>
       </c>
       <c r="R181" t="n">
-        <v>8.029999999999999</v>
+        <v>4.14</v>
       </c>
       <c r="S181" t="n">
-        <v>1.53</v>
+        <v>0.79</v>
       </c>
       <c r="T181" t="n">
-        <v>7.84</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="182">
@@ -13885,10 +13885,10 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0.61</v>
+        <v>0.83</v>
       </c>
       <c r="M182" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="N182" t="n">
         <v>0.61</v>
@@ -13897,19 +13897,19 @@
         <v>0.63</v>
       </c>
       <c r="P182" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.7595</v>
       </c>
       <c r="Q182" t="n">
         <v>2</v>
       </c>
       <c r="R182" t="n">
-        <v>8.550000000000001</v>
+        <v>3.64</v>
       </c>
       <c r="S182" t="n">
-        <v>1.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="T182" t="n">
-        <v>8.34</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="183">
@@ -13959,10 +13959,10 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0.54</v>
+        <v>0.77</v>
       </c>
       <c r="M183" t="n">
-        <v>0.58</v>
+        <v>0.79</v>
       </c>
       <c r="N183" t="n">
         <v>0.93</v>
@@ -13971,19 +13971,19 @@
         <v>0.63</v>
       </c>
       <c r="P183" t="n">
-        <v>0.6455</v>
+        <v>0.788</v>
       </c>
       <c r="Q183" t="n">
         <v>1</v>
       </c>
       <c r="R183" t="n">
-        <v>9.529999999999999</v>
+        <v>4.62</v>
       </c>
       <c r="S183" t="n">
-        <v>1.81</v>
+        <v>0.88</v>
       </c>
       <c r="T183" t="n">
-        <v>9.300000000000001</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="184">
@@ -14033,10 +14033,10 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0.49</v>
+        <v>0.73</v>
       </c>
       <c r="M184" t="n">
-        <v>0.53</v>
+        <v>0.74</v>
       </c>
       <c r="N184" t="n">
         <v>0.86</v>
@@ -14045,19 +14045,19 @@
         <v>0.63</v>
       </c>
       <c r="P184" t="n">
-        <v>0.599</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="Q184" t="n">
         <v>3</v>
       </c>
       <c r="R184" t="n">
-        <v>10.27</v>
+        <v>5.36</v>
       </c>
       <c r="S184" t="n">
-        <v>1.95</v>
+        <v>1.02</v>
       </c>
       <c r="T184" t="n">
-        <v>10.02</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="185">
@@ -14107,10 +14107,10 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0.7</v>
+        <v>0.96</v>
       </c>
       <c r="M185" t="n">
-        <v>0.7</v>
+        <v>0.96</v>
       </c>
       <c r="N185" t="n">
         <v>0.7</v>
@@ -14119,19 +14119,19 @@
         <v>0.75</v>
       </c>
       <c r="P185" t="n">
-        <v>0.7075</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="Q185" t="n">
         <v>2</v>
       </c>
       <c r="R185" t="n">
-        <v>7.39</v>
+        <v>1.63</v>
       </c>
       <c r="S185" t="n">
-        <v>1.4</v>
+        <v>0.31</v>
       </c>
       <c r="T185" t="n">
-        <v>7.53</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="186">
@@ -14181,10 +14181,10 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0.65</v>
+        <v>0.92</v>
       </c>
       <c r="M186" t="n">
-        <v>0.65</v>
+        <v>0.92</v>
       </c>
       <c r="N186" t="n">
         <v>0.93</v>
@@ -14193,19 +14193,19 @@
         <v>0.75</v>
       </c>
       <c r="P186" t="n">
-        <v>0.721</v>
+        <v>0.8965</v>
       </c>
       <c r="Q186" t="n">
         <v>1</v>
       </c>
       <c r="R186" t="n">
-        <v>8.08</v>
+        <v>2.32</v>
       </c>
       <c r="S186" t="n">
-        <v>1.54</v>
+        <v>0.44</v>
       </c>
       <c r="T186" t="n">
-        <v>8.24</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="187">
@@ -14255,10 +14255,10 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="M187" t="n">
-        <v>0.57</v>
+        <v>0.84</v>
       </c>
       <c r="N187" t="n">
         <v>0.7</v>
@@ -14267,19 +14267,19 @@
         <v>0.75</v>
       </c>
       <c r="P187" t="n">
-        <v>0.62</v>
+        <v>0.7985</v>
       </c>
       <c r="Q187" t="n">
         <v>3</v>
       </c>
       <c r="R187" t="n">
-        <v>9.25</v>
+        <v>3.49</v>
       </c>
       <c r="S187" t="n">
-        <v>1.76</v>
+        <v>0.66</v>
       </c>
       <c r="T187" t="n">
-        <v>9.43</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="188">
@@ -14329,10 +14329,10 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="N188" t="n">
         <v>0.61</v>
@@ -14341,19 +14341,19 @@
         <v>0.73</v>
       </c>
       <c r="P188" t="n">
-        <v>0.846</v>
+        <v>0.8815</v>
       </c>
       <c r="Q188" t="n">
         <v>3</v>
       </c>
       <c r="R188" t="n">
-        <v>3.88</v>
+        <v>0.15</v>
       </c>
       <c r="S188" t="n">
-        <v>0.74</v>
+        <v>0.03</v>
       </c>
       <c r="T188" t="n">
-        <v>3.79</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="189">
@@ -14403,10 +14403,10 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="N189" t="n">
         <v>0.86</v>
@@ -14415,19 +14415,19 @@
         <v>0.73</v>
       </c>
       <c r="P189" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.9315</v>
       </c>
       <c r="Q189" t="n">
         <v>1</v>
       </c>
       <c r="R189" t="n">
-        <v>4.36</v>
+        <v>0.63</v>
       </c>
       <c r="S189" t="n">
-        <v>0.83</v>
+        <v>0.12</v>
       </c>
       <c r="T189" t="n">
-        <v>4.25</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="190">
@@ -14477,10 +14477,10 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="M190" t="n">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="N190" t="n">
         <v>0.86</v>
@@ -14489,19 +14489,19 @@
         <v>0.73</v>
       </c>
       <c r="P190" t="n">
-        <v>0.8505</v>
+        <v>0.9185</v>
       </c>
       <c r="Q190" t="n">
         <v>2</v>
       </c>
       <c r="R190" t="n">
-        <v>4.99</v>
+        <v>1.26</v>
       </c>
       <c r="S190" t="n">
-        <v>0.95</v>
+        <v>0.24</v>
       </c>
       <c r="T190" t="n">
-        <v>4.87</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="191">
@@ -14551,10 +14551,10 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="M191" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="N191" t="n">
         <v>0.78</v>
@@ -14563,7 +14563,7 @@
         <v>0.85</v>
       </c>
       <c r="P191" t="n">
-        <v>0.719</v>
+        <v>0.6605</v>
       </c>
       <c r="Q191" t="n">
         <v>3</v>
@@ -14625,10 +14625,10 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="M192" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="N192" t="n">
         <v>0.93</v>
@@ -14637,7 +14637,7 @@
         <v>0.85</v>
       </c>
       <c r="P192" t="n">
-        <v>0.788</v>
+        <v>0.723</v>
       </c>
       <c r="Q192" t="n">
         <v>1</v>
@@ -14699,10 +14699,10 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="M193" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="N193" t="n">
         <v>0.7</v>
@@ -14711,7 +14711,7 @@
         <v>0.85</v>
       </c>
       <c r="P193" t="n">
-        <v>0.768</v>
+        <v>0.7</v>
       </c>
       <c r="Q193" t="n">
         <v>2</v>
@@ -14773,10 +14773,10 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="N194" t="n">
         <v>0.51</v>
@@ -14785,19 +14785,19 @@
         <v>0.72</v>
       </c>
       <c r="P194" t="n">
-        <v>0.8175</v>
+        <v>0.86</v>
       </c>
       <c r="Q194" t="n">
         <v>3</v>
       </c>
       <c r="R194" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="S194" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="T194" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -14847,10 +14847,10 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="N195" t="n">
         <v>0.78</v>
@@ -14859,19 +14859,19 @@
         <v>0.72</v>
       </c>
       <c r="P195" t="n">
-        <v>0.826</v>
+        <v>0.914</v>
       </c>
       <c r="Q195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R195" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="T195" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -14921,10 +14921,10 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="N196" t="n">
         <v>1</v>
@@ -14933,19 +14933,19 @@
         <v>0.72</v>
       </c>
       <c r="P196" t="n">
-        <v>0.8245</v>
+        <v>0.958</v>
       </c>
       <c r="Q196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R196" t="n">
-        <v>5.94</v>
+        <v>0.61</v>
       </c>
       <c r="S196" t="n">
-        <v>1.13</v>
+        <v>0.12</v>
       </c>
       <c r="T196" t="n">
-        <v>6.18</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="197">
@@ -14995,10 +14995,10 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="M197" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="N197" t="n">
         <v>0.45</v>
@@ -15007,7 +15007,7 @@
         <v>0.68</v>
       </c>
       <c r="P197" t="n">
-        <v>0.332</v>
+        <v>0.303</v>
       </c>
       <c r="Q197" t="n">
         <v>3</v>
@@ -15069,10 +15069,10 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="M198" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="N198" t="n">
         <v>0.93</v>
@@ -15081,7 +15081,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="P198" t="n">
-        <v>0.516</v>
+        <v>0.48</v>
       </c>
       <c r="Q198" t="n">
         <v>2</v>
@@ -15143,10 +15143,10 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="M199" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="N199" t="n">
         <v>0.67</v>
@@ -15155,7 +15155,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="P199" t="n">
-        <v>0.532</v>
+        <v>0.49</v>
       </c>
       <c r="Q199" t="n">
         <v>1</v>
@@ -15217,10 +15217,10 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0.47</v>
+        <v>0.76</v>
       </c>
       <c r="M200" t="n">
-        <v>0.48</v>
+        <v>0.76</v>
       </c>
       <c r="N200" t="n">
         <v>0.29</v>
@@ -15229,19 +15229,19 @@
         <v>0.6</v>
       </c>
       <c r="P200" t="n">
-        <v>0.457</v>
+        <v>0.642</v>
       </c>
       <c r="Q200" t="n">
         <v>2</v>
       </c>
       <c r="R200" t="n">
-        <v>10.58</v>
+        <v>4.82</v>
       </c>
       <c r="S200" t="n">
-        <v>2.01</v>
+        <v>0.92</v>
       </c>
       <c r="T200" t="n">
-        <v>10.79</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="201">
@@ -15291,10 +15291,10 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0.38</v>
+        <v>0.68</v>
       </c>
       <c r="M201" t="n">
-        <v>0.39</v>
+        <v>0.68</v>
       </c>
       <c r="N201" t="n">
         <v>0.78</v>
@@ -15303,19 +15303,19 @@
         <v>0.6</v>
       </c>
       <c r="P201" t="n">
-        <v>0.4965</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="Q201" t="n">
         <v>1</v>
       </c>
       <c r="R201" t="n">
-        <v>11.88</v>
+        <v>6.12</v>
       </c>
       <c r="S201" t="n">
-        <v>2.26</v>
+        <v>1.16</v>
       </c>
       <c r="T201" t="n">
-        <v>12.11</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="202">
@@ -15365,10 +15365,10 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>0.22</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M202" t="n">
-        <v>0.26</v>
+        <v>0.57</v>
       </c>
       <c r="N202" t="n">
         <v>0.7</v>
@@ -15377,19 +15377,19 @@
         <v>0.6</v>
       </c>
       <c r="P202" t="n">
-        <v>0.387</v>
+        <v>0.5975</v>
       </c>
       <c r="Q202" t="n">
         <v>3</v>
       </c>
       <c r="R202" t="n">
-        <v>13.71</v>
+        <v>7.94</v>
       </c>
       <c r="S202" t="n">
-        <v>2.6</v>
+        <v>1.51</v>
       </c>
       <c r="T202" t="n">
-        <v>13.97</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="203">
@@ -15439,10 +15439,10 @@
         </is>
       </c>
       <c r="L203" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M203" t="n">
         <v>0.03</v>
-      </c>
-      <c r="M203" t="n">
-        <v>0.05</v>
       </c>
       <c r="N203" t="n">
         <v>0.86</v>
@@ -15451,7 +15451,7 @@
         <v>0.76</v>
       </c>
       <c r="P203" t="n">
-        <v>0.3125</v>
+        <v>0.2995</v>
       </c>
       <c r="Q203" t="n">
         <v>3</v>
@@ -15513,10 +15513,10 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="M204" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="N204" t="n">
         <v>0.86</v>
@@ -15525,7 +15525,7 @@
         <v>0.76</v>
       </c>
       <c r="P204" t="n">
-        <v>0.3935</v>
+        <v>0.371</v>
       </c>
       <c r="Q204" t="n">
         <v>2</v>
@@ -15587,10 +15587,10 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="M205" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="N205" t="n">
         <v>0.51</v>
@@ -15599,7 +15599,7 @@
         <v>0.79</v>
       </c>
       <c r="P205" t="n">
-        <v>0.406</v>
+        <v>0.3735</v>
       </c>
       <c r="Q205" t="n">
         <v>1</v>
@@ -15661,10 +15661,10 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="M206" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="N206" t="n">
         <v>0.29</v>
@@ -15673,7 +15673,7 @@
         <v>0.68</v>
       </c>
       <c r="P206" t="n">
-        <v>0.706</v>
+        <v>0.6345</v>
       </c>
       <c r="Q206" t="n">
         <v>3</v>
@@ -15735,10 +15735,10 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="M207" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="N207" t="n">
         <v>0.51</v>
@@ -15747,7 +15747,7 @@
         <v>0.84</v>
       </c>
       <c r="P207" t="n">
-        <v>0.787</v>
+        <v>0.7125</v>
       </c>
       <c r="Q207" t="n">
         <v>2</v>
@@ -15809,10 +15809,10 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="M208" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="N208" t="n">
         <v>0.7</v>
@@ -15821,7 +15821,7 @@
         <v>0.91</v>
       </c>
       <c r="P208" t="n">
-        <v>0.845</v>
+        <v>0.7705</v>
       </c>
       <c r="Q208" t="n">
         <v>1</v>
@@ -15883,10 +15883,10 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="M209" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="N209" t="n">
         <v>0.61</v>
@@ -15895,19 +15895,19 @@
         <v>0.7</v>
       </c>
       <c r="P209" t="n">
-        <v>0.8085</v>
+        <v>0.8445</v>
       </c>
       <c r="Q209" t="n">
         <v>3</v>
       </c>
       <c r="R209" t="n">
-        <v>4.54</v>
+        <v>1.82</v>
       </c>
       <c r="S209" t="n">
-        <v>0.86</v>
+        <v>0.35</v>
       </c>
       <c r="T209" t="n">
-        <v>4.63</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="210">
@@ -15957,10 +15957,10 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="M210" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="N210" t="n">
         <v>0.86</v>
@@ -15969,19 +15969,19 @@
         <v>0.7</v>
       </c>
       <c r="P210" t="n">
-        <v>0.8425</v>
+        <v>0.8815</v>
       </c>
       <c r="Q210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R210" t="n">
-        <v>4.88</v>
+        <v>2.16</v>
       </c>
       <c r="S210" t="n">
-        <v>0.93</v>
+        <v>0.41</v>
       </c>
       <c r="T210" t="n">
-        <v>4.97</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="211">
@@ -16031,10 +16031,10 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="M211" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="N211" t="n">
         <v>0.93</v>
@@ -16043,19 +16043,19 @@
         <v>0.7</v>
       </c>
       <c r="P211" t="n">
-        <v>0.8435</v>
+        <v>0.879</v>
       </c>
       <c r="Q211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R211" t="n">
-        <v>5.22</v>
+        <v>2.5</v>
       </c>
       <c r="S211" t="n">
-        <v>0.99</v>
+        <v>0.48</v>
       </c>
       <c r="T211" t="n">
-        <v>5.32</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="212">
@@ -16105,10 +16105,10 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M212" t="n">
-        <v>0.59</v>
+        <v>0.82</v>
       </c>
       <c r="N212" t="n">
         <v>0</v>
@@ -16117,19 +16117,19 @@
         <v>0.72</v>
       </c>
       <c r="P212" t="n">
-        <v>0.4825</v>
+        <v>0.638</v>
       </c>
       <c r="Q212" t="n">
         <v>3</v>
       </c>
       <c r="R212" t="n">
-        <v>9.33</v>
+        <v>4.01</v>
       </c>
       <c r="S212" t="n">
-        <v>1.77</v>
+        <v>0.76</v>
       </c>
       <c r="T212" t="n">
-        <v>9.109999999999999</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="213">
@@ -16179,10 +16179,10 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0.51</v>
+        <v>0.77</v>
       </c>
       <c r="M213" t="n">
-        <v>0.55</v>
+        <v>0.78</v>
       </c>
       <c r="N213" t="n">
         <v>0.46</v>
@@ -16191,19 +16191,19 @@
         <v>0.72</v>
       </c>
       <c r="P213" t="n">
-        <v>0.5455</v>
+        <v>0.704</v>
       </c>
       <c r="Q213" t="n">
         <v>2</v>
       </c>
       <c r="R213" t="n">
-        <v>9.98</v>
+        <v>4.66</v>
       </c>
       <c r="S213" t="n">
-        <v>1.9</v>
+        <v>0.88</v>
       </c>
       <c r="T213" t="n">
-        <v>9.74</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="214">
@@ -16253,10 +16253,10 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="M214" t="n">
-        <v>0.51</v>
+        <v>0.75</v>
       </c>
       <c r="N214" t="n">
         <v>0.8100000000000001</v>
@@ -16265,19 +16265,19 @@
         <v>0.72</v>
       </c>
       <c r="P214" t="n">
-        <v>0.5895</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="Q214" t="n">
         <v>1</v>
       </c>
       <c r="R214" t="n">
-        <v>10.62</v>
+        <v>5.3</v>
       </c>
       <c r="S214" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="T214" t="n">
-        <v>10.37</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="215">
@@ -16345,13 +16345,13 @@
         <v>3</v>
       </c>
       <c r="R215" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S215" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="T215" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -16419,13 +16419,13 @@
         <v>2</v>
       </c>
       <c r="R216" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="S216" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="T216" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -16475,10 +16475,10 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="M217" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="N217" t="n">
         <v>1</v>
@@ -16487,19 +16487,19 @@
         <v>0.78</v>
       </c>
       <c r="P217" t="n">
-        <v>0.944</v>
+        <v>0.967</v>
       </c>
       <c r="Q217" t="n">
         <v>1</v>
       </c>
       <c r="R217" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S217" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="T217" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -16715,13 +16715,13 @@
         <v>1</v>
       </c>
       <c r="R220" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="S220" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T220" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -16789,13 +16789,13 @@
         <v>3</v>
       </c>
       <c r="R221" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S221" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="T221" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -16860,16 +16860,16 @@
         <v>0.929</v>
       </c>
       <c r="Q222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R222" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S222" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="T222" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -16919,10 +16919,10 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="M223" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="N223" t="n">
         <v>0.93</v>
@@ -16931,19 +16931,19 @@
         <v>0.82</v>
       </c>
       <c r="P223" t="n">
-        <v>0.92</v>
+        <v>0.959</v>
       </c>
       <c r="Q223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R223" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="S223" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="T223" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -17215,10 +17215,10 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="M227" t="n">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="N227" t="n">
         <v>0</v>
@@ -17227,7 +17227,7 @@
         <v>0.55</v>
       </c>
       <c r="P227" t="n">
-        <v>0.667</v>
+        <v>0.5895</v>
       </c>
       <c r="Q227" t="n">
         <v>3</v>
@@ -17289,10 +17289,10 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>0.95</v>
+        <v>0.83</v>
       </c>
       <c r="M228" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="N228" t="n">
         <v>0.7</v>
@@ -17301,7 +17301,7 @@
         <v>0.97</v>
       </c>
       <c r="P228" t="n">
-        <v>0.8995</v>
+        <v>0.8215</v>
       </c>
       <c r="Q228" t="n">
         <v>2</v>
@@ -17363,10 +17363,10 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="M229" t="n">
-        <v>0.99</v>
+        <v>0.86</v>
       </c>
       <c r="N229" t="n">
         <v>0.86</v>
@@ -17375,7 +17375,7 @@
         <v>0.93</v>
       </c>
       <c r="P229" t="n">
-        <v>0.958</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="Q229" t="n">
         <v>1</v>
@@ -17603,13 +17603,13 @@
         <v>1</v>
       </c>
       <c r="R232" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="S232" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T232" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -17659,10 +17659,10 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="M233" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="N233" t="n">
         <v>0.18</v>
@@ -17671,7 +17671,7 @@
         <v>0.64</v>
       </c>
       <c r="P233" t="n">
-        <v>0.639</v>
+        <v>0.574</v>
       </c>
       <c r="Q233" t="n">
         <v>3</v>
@@ -17733,10 +17733,10 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
       <c r="M234" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="N234" t="n">
         <v>0.67</v>
@@ -17745,7 +17745,7 @@
         <v>0.85</v>
       </c>
       <c r="P234" t="n">
-        <v>0.8105</v>
+        <v>0.736</v>
       </c>
       <c r="Q234" t="n">
         <v>2</v>
@@ -17807,10 +17807,10 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="M235" t="n">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="N235" t="n">
         <v>1</v>
@@ -17819,7 +17819,7 @@
         <v>0.85</v>
       </c>
       <c r="P235" t="n">
-        <v>0.9155</v>
+        <v>0.841</v>
       </c>
       <c r="Q235" t="n">
         <v>1</v>
@@ -17881,10 +17881,10 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
       <c r="M236" t="n">
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="N236" t="n">
         <v>0.7</v>
@@ -17893,7 +17893,7 @@
         <v>0.92</v>
       </c>
       <c r="P236" t="n">
-        <v>0.905</v>
+        <v>0.824</v>
       </c>
       <c r="Q236" t="n">
         <v>3</v>
@@ -17955,10 +17955,10 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="M237" t="n">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="N237" t="n">
         <v>1</v>
@@ -17967,7 +17967,7 @@
         <v>0.92</v>
       </c>
       <c r="P237" t="n">
-        <v>0.978</v>
+        <v>0.894</v>
       </c>
       <c r="Q237" t="n">
         <v>1</v>
@@ -18029,10 +18029,10 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="M238" t="n">
-        <v>0.99</v>
+        <v>0.87</v>
       </c>
       <c r="N238" t="n">
         <v>0.78</v>
@@ -18041,7 +18041,7 @@
         <v>0.92</v>
       </c>
       <c r="P238" t="n">
-        <v>0.9405</v>
+        <v>0.8595</v>
       </c>
       <c r="Q238" t="n">
         <v>2</v>
@@ -18103,10 +18103,10 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="M239" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="N239" t="n">
         <v>1</v>
@@ -18115,7 +18115,7 @@
         <v>0.89</v>
       </c>
       <c r="P239" t="n">
-        <v>0.8955</v>
+        <v>0.824</v>
       </c>
       <c r="Q239" t="n">
         <v>1</v>
@@ -18177,10 +18177,10 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="M240" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="N240" t="n">
         <v>0.7</v>
@@ -18189,7 +18189,7 @@
         <v>0.89</v>
       </c>
       <c r="P240" t="n">
-        <v>0.8615</v>
+        <v>0.7835</v>
       </c>
       <c r="Q240" t="n">
         <v>2</v>
@@ -18251,10 +18251,10 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M241" t="n">
-        <v>0.92</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N241" t="n">
         <v>0.41</v>
@@ -18263,7 +18263,7 @@
         <v>0.78</v>
       </c>
       <c r="P241" t="n">
-        <v>0.8</v>
+        <v>0.7255</v>
       </c>
       <c r="Q241" t="n">
         <v>3</v>
@@ -18325,10 +18325,10 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="M242" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="N242" t="n">
         <v>0.86</v>
@@ -18337,7 +18337,7 @@
         <v>0.86</v>
       </c>
       <c r="P242" t="n">
-        <v>0.912</v>
+        <v>0.834</v>
       </c>
       <c r="Q242" t="n">
         <v>2</v>
@@ -18399,10 +18399,10 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
       <c r="M243" t="n">
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="N243" t="n">
         <v>0.93</v>
@@ -18411,7 +18411,7 @@
         <v>0.86</v>
       </c>
       <c r="P243" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.861</v>
       </c>
       <c r="Q243" t="n">
         <v>1</v>
@@ -18473,10 +18473,10 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="M244" t="n">
-        <v>0.99</v>
+        <v>0.87</v>
       </c>
       <c r="N244" t="n">
         <v>0.61</v>
@@ -18485,7 +18485,7 @@
         <v>0.86</v>
       </c>
       <c r="P244" t="n">
-        <v>0.8975</v>
+        <v>0.8165</v>
       </c>
       <c r="Q244" t="n">
         <v>3</v>
@@ -18547,10 +18547,10 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="M245" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="N245" t="n">
         <v>0.92</v>
@@ -18559,7 +18559,7 @@
         <v>0.9</v>
       </c>
       <c r="P245" t="n">
-        <v>0.7575</v>
+        <v>0.696</v>
       </c>
       <c r="Q245" t="n">
         <v>1</v>
@@ -18621,10 +18621,10 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="M246" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="N246" t="n">
         <v>0.51</v>
@@ -18633,7 +18633,7 @@
         <v>0.9</v>
       </c>
       <c r="P246" t="n">
-        <v>0.7145</v>
+        <v>0.6465</v>
       </c>
       <c r="Q246" t="n">
         <v>2</v>
@@ -18695,10 +18695,10 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="M247" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="N247" t="n">
         <v>0.06</v>
@@ -18707,7 +18707,7 @@
         <v>0.67</v>
       </c>
       <c r="P247" t="n">
-        <v>0.616</v>
+        <v>0.548</v>
       </c>
       <c r="Q247" t="n">
         <v>3</v>
@@ -18769,10 +18769,10 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="M248" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="N248" t="n">
         <v>0.67</v>
@@ -18781,7 +18781,7 @@
         <v>0.84</v>
       </c>
       <c r="P248" t="n">
-        <v>0.7085</v>
+        <v>0.647</v>
       </c>
       <c r="Q248" t="n">
         <v>3</v>
@@ -18843,10 +18843,10 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
       <c r="M249" t="n">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
       <c r="N249" t="n">
         <v>1</v>
@@ -18855,7 +18855,7 @@
         <v>0.84</v>
       </c>
       <c r="P249" t="n">
-        <v>0.794</v>
+        <v>0.729</v>
       </c>
       <c r="Q249" t="n">
         <v>1</v>
@@ -18917,10 +18917,10 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="M250" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="N250" t="n">
         <v>0.67</v>
@@ -18929,7 +18929,7 @@
         <v>0.92</v>
       </c>
       <c r="P250" t="n">
-        <v>0.7595</v>
+        <v>0.6945</v>
       </c>
       <c r="Q250" t="n">
         <v>2</v>
@@ -18991,10 +18991,10 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="M251" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="N251" t="n">
         <v>0.86</v>
@@ -19003,7 +19003,7 @@
         <v>0.77</v>
       </c>
       <c r="P251" t="n">
-        <v>0.843</v>
+        <v>0.7685</v>
       </c>
       <c r="Q251" t="n">
         <v>1</v>
@@ -19065,10 +19065,10 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="M252" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="N252" t="n">
         <v>0.61</v>
@@ -19077,7 +19077,7 @@
         <v>0.84</v>
       </c>
       <c r="P252" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.7385</v>
       </c>
       <c r="Q252" t="n">
         <v>2</v>
@@ -19139,10 +19139,10 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="M253" t="n">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="N253" t="n">
         <v>0.29</v>
@@ -19151,7 +19151,7 @@
         <v>0.63</v>
       </c>
       <c r="P253" t="n">
-        <v>0.7275</v>
+        <v>0.653</v>
       </c>
       <c r="Q253" t="n">
         <v>3</v>
@@ -19213,10 +19213,10 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="M254" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="N254" t="n">
         <v>0.73</v>
@@ -19225,7 +19225,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="P254" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.515</v>
       </c>
       <c r="Q254" t="n">
         <v>3</v>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="M255" t="n">
-        <v>0.53</v>
+        <v>0.45</v>
       </c>
       <c r="N255" t="n">
         <v>0.92</v>
@@ -19299,7 +19299,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="P255" t="n">
-        <v>0.647</v>
+        <v>0.595</v>
       </c>
       <c r="Q255" t="n">
         <v>1</v>
@@ -19361,10 +19361,10 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="M256" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="N256" t="n">
         <v>0.51</v>
@@ -19373,7 +19373,7 @@
         <v>0.84</v>
       </c>
       <c r="P256" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="Q256" t="n">
         <v>2</v>
@@ -19435,10 +19435,10 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>0.71</v>
+        <v>0.93</v>
       </c>
       <c r="M257" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="N257" t="n">
         <v>0.15</v>
@@ -19447,19 +19447,19 @@
         <v>0.65</v>
       </c>
       <c r="P257" t="n">
-        <v>0.5855</v>
+        <v>0.7285</v>
       </c>
       <c r="Q257" t="n">
         <v>3</v>
       </c>
       <c r="R257" t="n">
-        <v>7.26</v>
+        <v>2.17</v>
       </c>
       <c r="S257" t="n">
-        <v>1.38</v>
+        <v>0.41</v>
       </c>
       <c r="T257" t="n">
-        <v>7.56</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="258">
@@ -19509,10 +19509,10 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="M258" t="n">
-        <v>0.61</v>
+        <v>0.85</v>
       </c>
       <c r="N258" t="n">
         <v>0.61</v>
@@ -19521,19 +19521,19 @@
         <v>0.65</v>
       </c>
       <c r="P258" t="n">
-        <v>0.619</v>
+        <v>0.772</v>
       </c>
       <c r="Q258" t="n">
         <v>2</v>
       </c>
       <c r="R258" t="n">
-        <v>8.49</v>
+        <v>3.4</v>
       </c>
       <c r="S258" t="n">
-        <v>1.61</v>
+        <v>0.65</v>
       </c>
       <c r="T258" t="n">
-        <v>8.84</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="259">
@@ -19583,10 +19583,10 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>0.55</v>
+        <v>0.79</v>
       </c>
       <c r="M259" t="n">
-        <v>0.55</v>
+        <v>0.79</v>
       </c>
       <c r="N259" t="n">
         <v>0.86</v>
@@ -19595,19 +19595,19 @@
         <v>0.65</v>
       </c>
       <c r="P259" t="n">
-        <v>0.627</v>
+        <v>0.783</v>
       </c>
       <c r="Q259" t="n">
         <v>1</v>
       </c>
       <c r="R259" t="n">
-        <v>9.41</v>
+        <v>4.32</v>
       </c>
       <c r="S259" t="n">
-        <v>1.79</v>
+        <v>0.82</v>
       </c>
       <c r="T259" t="n">
-        <v>9.789999999999999</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="260">
@@ -19675,13 +19675,13 @@
         <v>3</v>
       </c>
       <c r="R260" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S260" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="T260" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -19749,13 +19749,13 @@
         <v>2</v>
       </c>
       <c r="R261" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S261" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="T261" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -19823,13 +19823,13 @@
         <v>1</v>
       </c>
       <c r="R262" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S262" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="T262" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -19879,10 +19879,10 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="M263" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="N263" t="n">
         <v>0</v>
@@ -19891,19 +19891,19 @@
         <v>0.29</v>
       </c>
       <c r="P263" t="n">
-        <v>0.495</v>
+        <v>0.599</v>
       </c>
       <c r="Q263" t="n">
         <v>3</v>
       </c>
       <c r="R263" t="n">
-        <v>7.27</v>
+        <v>3.29</v>
       </c>
       <c r="S263" t="n">
-        <v>1.38</v>
+        <v>0.63</v>
       </c>
       <c r="T263" t="n">
-        <v>7.57</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="264">
@@ -19953,10 +19953,10 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>0.66</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M264" t="n">
-        <v>0.65</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N264" t="n">
         <v>0.29</v>
@@ -19965,19 +19965,19 @@
         <v>0.62</v>
       </c>
       <c r="P264" t="n">
-        <v>0.5765</v>
+        <v>0.6775</v>
       </c>
       <c r="Q264" t="n">
         <v>2</v>
       </c>
       <c r="R264" t="n">
-        <v>7.95</v>
+        <v>3.98</v>
       </c>
       <c r="S264" t="n">
-        <v>1.51</v>
+        <v>0.76</v>
       </c>
       <c r="T264" t="n">
-        <v>8.279999999999999</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="265">
@@ -20027,10 +20027,10 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>0.61</v>
+        <v>0.77</v>
       </c>
       <c r="M265" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="N265" t="n">
         <v>0.61</v>
@@ -20039,19 +20039,19 @@
         <v>0.62</v>
       </c>
       <c r="P265" t="n">
-        <v>0.608</v>
+        <v>0.7155</v>
       </c>
       <c r="Q265" t="n">
         <v>1</v>
       </c>
       <c r="R265" t="n">
-        <v>8.630000000000001</v>
+        <v>4.66</v>
       </c>
       <c r="S265" t="n">
-        <v>1.64</v>
+        <v>0.89</v>
       </c>
       <c r="T265" t="n">
-        <v>8.99</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="266">
@@ -20101,10 +20101,10 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="M266" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="N266" t="n">
         <v>0.78</v>
@@ -20113,7 +20113,7 @@
         <v>0.84</v>
       </c>
       <c r="P266" t="n">
-        <v>0.7175</v>
+        <v>0.659</v>
       </c>
       <c r="Q266" t="n">
         <v>3</v>
@@ -20175,10 +20175,10 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M267" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="N267" t="n">
         <v>1</v>
@@ -20187,7 +20187,7 @@
         <v>0.84</v>
       </c>
       <c r="P267" t="n">
-        <v>0.781</v>
+        <v>0.7195</v>
       </c>
       <c r="Q267" t="n">
         <v>1</v>
@@ -20249,10 +20249,10 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="M268" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="N268" t="n">
         <v>0.78</v>
@@ -20261,7 +20261,7 @@
         <v>0.88</v>
       </c>
       <c r="P268" t="n">
-        <v>0.7625</v>
+        <v>0.701</v>
       </c>
       <c r="Q268" t="n">
         <v>2</v>
@@ -20323,10 +20323,10 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="M269" t="n">
-        <v>0.76</v>
+        <v>0.92</v>
       </c>
       <c r="N269" t="n">
         <v>0</v>
@@ -20335,19 +20335,19 @@
         <v>0.29</v>
       </c>
       <c r="P269" t="n">
-        <v>0.5435</v>
+        <v>0.6415</v>
       </c>
       <c r="Q269" t="n">
         <v>3</v>
       </c>
       <c r="R269" t="n">
-        <v>6.27</v>
+        <v>2.27</v>
       </c>
       <c r="S269" t="n">
-        <v>1.19</v>
+        <v>0.43</v>
       </c>
       <c r="T269" t="n">
-        <v>6.53</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="270">
@@ -20397,10 +20397,10 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="M270" t="n">
-        <v>0.72</v>
+        <v>0.87</v>
       </c>
       <c r="N270" t="n">
         <v>0.29</v>
@@ -20409,19 +20409,19 @@
         <v>0.61</v>
       </c>
       <c r="P270" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.718</v>
       </c>
       <c r="Q270" t="n">
         <v>2</v>
       </c>
       <c r="R270" t="n">
-        <v>6.96</v>
+        <v>2.96</v>
       </c>
       <c r="S270" t="n">
-        <v>1.32</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T270" t="n">
-        <v>7.24</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="271">
@@ -20471,10 +20471,10 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>0.68</v>
+        <v>0.83</v>
       </c>
       <c r="M271" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="N271" t="n">
         <v>0.61</v>
@@ -20483,19 +20483,19 @@
         <v>0.61</v>
       </c>
       <c r="P271" t="n">
-        <v>0.652</v>
+        <v>0.753</v>
       </c>
       <c r="Q271" t="n">
         <v>1</v>
       </c>
       <c r="R271" t="n">
-        <v>7.65</v>
+        <v>3.65</v>
       </c>
       <c r="S271" t="n">
-        <v>1.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="T271" t="n">
-        <v>7.96</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="272">
@@ -20545,10 +20545,10 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="M272" t="n">
-        <v>0.39</v>
+        <v>0.33</v>
       </c>
       <c r="N272" t="n">
         <v>1</v>
@@ -20557,7 +20557,7 @@
         <v>0.8</v>
       </c>
       <c r="P272" t="n">
-        <v>0.5705</v>
+        <v>0.5315</v>
       </c>
       <c r="Q272" t="n">
         <v>1</v>
@@ -20619,10 +20619,10 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="M273" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="N273" t="n">
         <v>0.76</v>
@@ -20631,7 +20631,7 @@
         <v>0.8</v>
       </c>
       <c r="P273" t="n">
-        <v>0.5615</v>
+        <v>0.516</v>
       </c>
       <c r="Q273" t="n">
         <v>2</v>
@@ -20693,10 +20693,10 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="M274" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="N274" t="n">
         <v>0.45</v>
@@ -20705,7 +20705,7 @@
         <v>0.8</v>
       </c>
       <c r="P274" t="n">
-        <v>0.535</v>
+        <v>0.4865</v>
       </c>
       <c r="Q274" t="n">
         <v>3</v>
@@ -20767,10 +20767,10 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M275" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="N275" t="n">
         <v>0.41</v>
@@ -20779,19 +20779,19 @@
         <v>0.64</v>
       </c>
       <c r="P275" t="n">
-        <v>0.6655</v>
+        <v>0.828</v>
       </c>
       <c r="Q275" t="n">
         <v>3</v>
       </c>
       <c r="R275" t="n">
-        <v>6.67</v>
+        <v>0.97</v>
       </c>
       <c r="S275" t="n">
-        <v>1.27</v>
+        <v>0.18</v>
       </c>
       <c r="T275" t="n">
-        <v>6.8</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="276">
@@ -20841,10 +20841,10 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="M276" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="N276" t="n">
         <v>0.7</v>
@@ -20853,19 +20853,19 @@
         <v>0.64</v>
       </c>
       <c r="P276" t="n">
-        <v>0.6845</v>
+        <v>0.8535</v>
       </c>
       <c r="Q276" t="n">
         <v>2</v>
       </c>
       <c r="R276" t="n">
-        <v>7.44</v>
+        <v>1.74</v>
       </c>
       <c r="S276" t="n">
-        <v>1.41</v>
+        <v>0.33</v>
       </c>
       <c r="T276" t="n">
-        <v>7.59</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="277">
@@ -20915,10 +20915,10 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>0.64</v>
+        <v>0.9</v>
       </c>
       <c r="M277" t="n">
-        <v>0.64</v>
+        <v>0.9</v>
       </c>
       <c r="N277" t="n">
         <v>0.93</v>
@@ -20927,19 +20927,19 @@
         <v>0.64</v>
       </c>
       <c r="P277" t="n">
-        <v>0.698</v>
+        <v>0.867</v>
       </c>
       <c r="Q277" t="n">
         <v>1</v>
       </c>
       <c r="R277" t="n">
-        <v>8.220000000000001</v>
+        <v>2.52</v>
       </c>
       <c r="S277" t="n">
-        <v>1.56</v>
+        <v>0.48</v>
       </c>
       <c r="T277" t="n">
-        <v>8.380000000000001</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="278">
@@ -20989,10 +20989,10 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>0.36</v>
+        <v>0.72</v>
       </c>
       <c r="M278" t="n">
-        <v>0.37</v>
+        <v>0.73</v>
       </c>
       <c r="N278" t="n">
         <v>0.02</v>
@@ -21001,19 +21001,19 @@
         <v>0.52</v>
       </c>
       <c r="P278" t="n">
-        <v>0.3195</v>
+        <v>0.5535</v>
       </c>
       <c r="Q278" t="n">
         <v>3</v>
       </c>
       <c r="R278" t="n">
-        <v>12.11</v>
+        <v>5.39</v>
       </c>
       <c r="S278" t="n">
-        <v>2.3</v>
+        <v>1.02</v>
       </c>
       <c r="T278" t="n">
-        <v>12.34</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="279">
@@ -21063,10 +21063,10 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>0.28</v>
+        <v>0.65</v>
       </c>
       <c r="M279" t="n">
-        <v>0.3</v>
+        <v>0.66</v>
       </c>
       <c r="N279" t="n">
         <v>0.45</v>
@@ -21075,19 +21075,19 @@
         <v>0.62</v>
       </c>
       <c r="P279" t="n">
-        <v>0.372</v>
+        <v>0.609</v>
       </c>
       <c r="Q279" t="n">
         <v>2</v>
       </c>
       <c r="R279" t="n">
-        <v>13.21</v>
+        <v>6.49</v>
       </c>
       <c r="S279" t="n">
-        <v>2.51</v>
+        <v>1.23</v>
       </c>
       <c r="T279" t="n">
-        <v>13.46</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="280">
@@ -21137,10 +21137,10 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>0.18</v>
+        <v>0.59</v>
       </c>
       <c r="M280" t="n">
-        <v>0.22</v>
+        <v>0.59</v>
       </c>
       <c r="N280" t="n">
         <v>0.76</v>
@@ -21149,19 +21149,19 @@
         <v>0.62</v>
       </c>
       <c r="P280" t="n">
-        <v>0.376</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="Q280" t="n">
         <v>1</v>
       </c>
       <c r="R280" t="n">
-        <v>14.31</v>
+        <v>7.59</v>
       </c>
       <c r="S280" t="n">
-        <v>2.72</v>
+        <v>1.44</v>
       </c>
       <c r="T280" t="n">
-        <v>14.58</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="281">
@@ -21211,10 +21211,10 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>0.73</v>
+        <v>0.86</v>
       </c>
       <c r="M281" t="n">
-        <v>0.72</v>
+        <v>0.86</v>
       </c>
       <c r="N281" t="n">
         <v>0</v>
@@ -21223,19 +21223,19 @@
         <v>0.15</v>
       </c>
       <c r="P281" t="n">
-        <v>0.4935</v>
+        <v>0.5815</v>
       </c>
       <c r="Q281" t="n">
         <v>3</v>
       </c>
       <c r="R281" t="n">
-        <v>6.88</v>
+        <v>3.18</v>
       </c>
       <c r="S281" t="n">
-        <v>1.31</v>
+        <v>0.6</v>
       </c>
       <c r="T281" t="n">
-        <v>7.16</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="282">
@@ -21285,10 +21285,10 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="M282" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="N282" t="n">
         <v>0</v>
@@ -21297,19 +21297,19 @@
         <v>0.4</v>
       </c>
       <c r="P282" t="n">
-        <v>0.505</v>
+        <v>0.593</v>
       </c>
       <c r="Q282" t="n">
         <v>2</v>
       </c>
       <c r="R282" t="n">
-        <v>7.51</v>
+        <v>3.81</v>
       </c>
       <c r="S282" t="n">
-        <v>1.43</v>
+        <v>0.72</v>
       </c>
       <c r="T282" t="n">
-        <v>7.82</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="283">
@@ -21359,10 +21359,10 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>0.64</v>
+        <v>0.78</v>
       </c>
       <c r="M283" t="n">
-        <v>0.63</v>
+        <v>0.78</v>
       </c>
       <c r="N283" t="n">
         <v>0.41</v>
@@ -21371,19 +21371,19 @@
         <v>0.6</v>
       </c>
       <c r="P283" t="n">
-        <v>0.5845</v>
+        <v>0.679</v>
       </c>
       <c r="Q283" t="n">
         <v>1</v>
       </c>
       <c r="R283" t="n">
-        <v>8.140000000000001</v>
+        <v>4.44</v>
       </c>
       <c r="S283" t="n">
-        <v>1.55</v>
+        <v>0.84</v>
       </c>
       <c r="T283" t="n">
-        <v>8.470000000000001</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="284">
@@ -21433,10 +21433,10 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="M284" t="n">
-        <v>0.79</v>
+        <v>0.98</v>
       </c>
       <c r="N284" t="n">
         <v>0.41</v>
@@ -21445,19 +21445,19 @@
         <v>0.64</v>
       </c>
       <c r="P284" t="n">
-        <v>0.6945</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="Q284" t="n">
         <v>3</v>
       </c>
       <c r="R284" t="n">
-        <v>5.99</v>
+        <v>1.32</v>
       </c>
       <c r="S284" t="n">
-        <v>1.14</v>
+        <v>0.25</v>
       </c>
       <c r="T284" t="n">
-        <v>6.11</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="285">
@@ -21507,10 +21507,10 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>0.74</v>
+        <v>0.93</v>
       </c>
       <c r="M285" t="n">
-        <v>0.74</v>
+        <v>0.93</v>
       </c>
       <c r="N285" t="n">
         <v>0.7</v>
@@ -21519,19 +21519,19 @@
         <v>0.64</v>
       </c>
       <c r="P285" t="n">
-        <v>0.717</v>
+        <v>0.8405</v>
       </c>
       <c r="Q285" t="n">
         <v>2</v>
       </c>
       <c r="R285" t="n">
-        <v>6.73</v>
+        <v>2.05</v>
       </c>
       <c r="S285" t="n">
-        <v>1.28</v>
+        <v>0.39</v>
       </c>
       <c r="T285" t="n">
-        <v>6.86</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="286">
@@ -21581,10 +21581,10 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="M286" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="N286" t="n">
         <v>0.93</v>
@@ -21593,19 +21593,19 @@
         <v>0.64</v>
       </c>
       <c r="P286" t="n">
-        <v>0.7305</v>
+        <v>0.8605</v>
       </c>
       <c r="Q286" t="n">
         <v>1</v>
       </c>
       <c r="R286" t="n">
-        <v>7.47</v>
+        <v>2.79</v>
       </c>
       <c r="S286" t="n">
-        <v>1.42</v>
+        <v>0.53</v>
       </c>
       <c r="T286" t="n">
-        <v>7.61</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="287">
@@ -21655,10 +21655,10 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>0.74</v>
+        <v>0.91</v>
       </c>
       <c r="M287" t="n">
-        <v>0.76</v>
+        <v>0.92</v>
       </c>
       <c r="N287" t="n">
         <v>0</v>
@@ -21667,19 +21667,19 @@
         <v>0.31</v>
       </c>
       <c r="P287" t="n">
-        <v>0.5345</v>
+        <v>0.6415</v>
       </c>
       <c r="Q287" t="n">
         <v>3</v>
       </c>
       <c r="R287" t="n">
-        <v>6.71</v>
+        <v>2.38</v>
       </c>
       <c r="S287" t="n">
-        <v>1.27</v>
+        <v>0.45</v>
       </c>
       <c r="T287" t="n">
-        <v>6.55</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="288">
@@ -21729,10 +21729,10 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="M288" t="n">
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
       <c r="N288" t="n">
         <v>0.29</v>
@@ -21741,19 +21741,19 @@
         <v>0.65</v>
       </c>
       <c r="P288" t="n">
-        <v>0.624</v>
+        <v>0.731</v>
       </c>
       <c r="Q288" t="n">
         <v>2</v>
       </c>
       <c r="R288" t="n">
-        <v>7.26</v>
+        <v>2.94</v>
       </c>
       <c r="S288" t="n">
-        <v>1.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T288" t="n">
-        <v>7.09</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="289">
@@ -21803,10 +21803,10 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>0.67</v>
+        <v>0.84</v>
       </c>
       <c r="M289" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="N289" t="n">
         <v>0.61</v>
@@ -21815,19 +21815,19 @@
         <v>0.65</v>
       </c>
       <c r="P289" t="n">
-        <v>0.662</v>
+        <v>0.769</v>
       </c>
       <c r="Q289" t="n">
         <v>1</v>
       </c>
       <c r="R289" t="n">
-        <v>7.81</v>
+        <v>3.49</v>
       </c>
       <c r="S289" t="n">
-        <v>1.48</v>
+        <v>0.66</v>
       </c>
       <c r="T289" t="n">
-        <v>7.62</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="290">
@@ -21880,7 +21880,7 @@
         <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="N290" t="n">
         <v>0.15</v>
@@ -21889,19 +21889,19 @@
         <v>0.49</v>
       </c>
       <c r="P290" t="n">
-        <v>0.1035</v>
+        <v>0.114</v>
       </c>
       <c r="Q290" t="n">
         <v>3</v>
       </c>
       <c r="R290" t="n">
-        <v>22.57</v>
+        <v>16.82</v>
       </c>
       <c r="S290" t="n">
-        <v>4.29</v>
+        <v>3.2</v>
       </c>
       <c r="T290" t="n">
-        <v>23</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="291">
@@ -21969,13 +21969,13 @@
         <v>2</v>
       </c>
       <c r="R291" t="n">
-        <v>23.94</v>
+        <v>18.19</v>
       </c>
       <c r="S291" t="n">
-        <v>4.55</v>
+        <v>3.46</v>
       </c>
       <c r="T291" t="n">
-        <v>24.4</v>
+        <v>18.55</v>
       </c>
     </row>
     <row r="292">
@@ -22043,13 +22043,13 @@
         <v>1</v>
       </c>
       <c r="R292" t="n">
-        <v>25.32</v>
+        <v>19.57</v>
       </c>
       <c r="S292" t="n">
-        <v>4.81</v>
+        <v>3.72</v>
       </c>
       <c r="T292" t="n">
-        <v>25.81</v>
+        <v>19.95</v>
       </c>
     </row>
     <row r="293">
@@ -22099,10 +22099,10 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>0.77</v>
+        <v>0.95</v>
       </c>
       <c r="M293" t="n">
-        <v>0.75</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N293" t="n">
         <v>0</v>
@@ -22111,19 +22111,19 @@
         <v>0.29</v>
       </c>
       <c r="P293" t="n">
-        <v>0.537</v>
+        <v>0.6575</v>
       </c>
       <c r="Q293" t="n">
         <v>3</v>
       </c>
       <c r="R293" t="n">
-        <v>6.42</v>
+        <v>1.85</v>
       </c>
       <c r="S293" t="n">
-        <v>1.22</v>
+        <v>0.35</v>
       </c>
       <c r="T293" t="n">
-        <v>6.68</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="294">
@@ -22173,10 +22173,10 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
       <c r="M294" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="N294" t="n">
         <v>0.29</v>
@@ -22185,19 +22185,19 @@
         <v>0.62</v>
       </c>
       <c r="P294" t="n">
-        <v>0.609</v>
+        <v>0.736</v>
       </c>
       <c r="Q294" t="n">
         <v>2</v>
       </c>
       <c r="R294" t="n">
-        <v>7.14</v>
+        <v>2.57</v>
       </c>
       <c r="S294" t="n">
-        <v>1.36</v>
+        <v>0.49</v>
       </c>
       <c r="T294" t="n">
-        <v>7.43</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="295">
@@ -22247,10 +22247,10 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>0.66</v>
+        <v>0.86</v>
       </c>
       <c r="M295" t="n">
-        <v>0.65</v>
+        <v>0.85</v>
       </c>
       <c r="N295" t="n">
         <v>0.61</v>
@@ -22259,19 +22259,19 @@
         <v>0.62</v>
       </c>
       <c r="P295" t="n">
-        <v>0.6405</v>
+        <v>0.7705</v>
       </c>
       <c r="Q295" t="n">
         <v>1</v>
       </c>
       <c r="R295" t="n">
-        <v>7.86</v>
+        <v>3.29</v>
       </c>
       <c r="S295" t="n">
-        <v>1.49</v>
+        <v>0.62</v>
       </c>
       <c r="T295" t="n">
-        <v>8.18</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="296">
@@ -22339,13 +22339,13 @@
         <v>3</v>
       </c>
       <c r="R296" t="n">
-        <v>26.76</v>
+        <v>18.87</v>
       </c>
       <c r="S296" t="n">
-        <v>5.08</v>
+        <v>3.58</v>
       </c>
       <c r="T296" t="n">
-        <v>27.27</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="297">
@@ -22413,13 +22413,13 @@
         <v>2</v>
       </c>
       <c r="R297" t="n">
-        <v>28.64</v>
+        <v>20.75</v>
       </c>
       <c r="S297" t="n">
-        <v>5.44</v>
+        <v>3.94</v>
       </c>
       <c r="T297" t="n">
-        <v>29.2</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="298">
@@ -22487,13 +22487,13 @@
         <v>1</v>
       </c>
       <c r="R298" t="n">
-        <v>30.53</v>
+        <v>22.64</v>
       </c>
       <c r="S298" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="T298" t="n">
-        <v>31.12</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="299">
@@ -22543,10 +22543,10 @@
         </is>
       </c>
       <c r="L299" t="n">
-        <v>0.64</v>
+        <v>0.54</v>
       </c>
       <c r="M299" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="N299" t="n">
         <v>0.78</v>
@@ -22555,7 +22555,7 @@
         <v>0.84</v>
       </c>
       <c r="P299" t="n">
-        <v>0.698</v>
+        <v>0.6365</v>
       </c>
       <c r="Q299" t="n">
         <v>3</v>
@@ -22617,10 +22617,10 @@
         </is>
       </c>
       <c r="L300" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M300" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="N300" t="n">
         <v>1</v>
@@ -22629,7 +22629,7 @@
         <v>0.84</v>
       </c>
       <c r="P300" t="n">
-        <v>0.7615</v>
+        <v>0.7</v>
       </c>
       <c r="Q300" t="n">
         <v>1</v>
@@ -22691,10 +22691,10 @@
         </is>
       </c>
       <c r="L301" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M301" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="N301" t="n">
         <v>0.78</v>
@@ -22703,7 +22703,7 @@
         <v>0.84</v>
       </c>
       <c r="P301" t="n">
-        <v>0.737</v>
+        <v>0.6755</v>
       </c>
       <c r="Q301" t="n">
         <v>2</v>
@@ -22765,10 +22765,10 @@
         </is>
       </c>
       <c r="L302" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M302" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="N302" t="n">
         <v>0.86</v>
@@ -22777,7 +22777,7 @@
         <v>0.82</v>
       </c>
       <c r="P302" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="Q302" t="n">
         <v>1</v>
@@ -22839,10 +22839,10 @@
         </is>
       </c>
       <c r="L303" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="M303" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="N303" t="n">
         <v>0.61</v>
@@ -22851,7 +22851,7 @@
         <v>0.82</v>
       </c>
       <c r="P303" t="n">
-        <v>0.7745</v>
+        <v>0.7065</v>
       </c>
       <c r="Q303" t="n">
         <v>2</v>
@@ -22913,10 +22913,10 @@
         </is>
       </c>
       <c r="L304" t="n">
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
       <c r="M304" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="N304" t="n">
         <v>0.29</v>
@@ -22925,7 +22925,7 @@
         <v>0.64</v>
       </c>
       <c r="P304" t="n">
-        <v>0.703</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="Q304" t="n">
         <v>3</v>
@@ -22987,10 +22987,10 @@
         </is>
       </c>
       <c r="L305" t="n">
-        <v>0.51</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M305" t="n">
-        <v>0.51</v>
+        <v>0.68</v>
       </c>
       <c r="N305" t="n">
         <v>0</v>
@@ -22999,19 +22999,19 @@
         <v>0.25</v>
       </c>
       <c r="P305" t="n">
-        <v>0.369</v>
+        <v>0.4825</v>
       </c>
       <c r="Q305" t="n">
         <v>3</v>
       </c>
       <c r="R305" t="n">
-        <v>9.9</v>
+        <v>5.96</v>
       </c>
       <c r="S305" t="n">
-        <v>1.88</v>
+        <v>1.13</v>
       </c>
       <c r="T305" t="n">
-        <v>10.31</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="306">
@@ -23061,10 +23061,10 @@
         </is>
       </c>
       <c r="L306" t="n">
-        <v>0.34</v>
+        <v>0.62</v>
       </c>
       <c r="M306" t="n">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="N306" t="n">
         <v>0.41</v>
@@ -23073,19 +23073,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="P306" t="n">
-        <v>0.422</v>
+        <v>0.569</v>
       </c>
       <c r="Q306" t="n">
         <v>2</v>
       </c>
       <c r="R306" t="n">
-        <v>10.96</v>
+        <v>7.02</v>
       </c>
       <c r="S306" t="n">
-        <v>2.08</v>
+        <v>1.33</v>
       </c>
       <c r="T306" t="n">
-        <v>11.41</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="307">
@@ -23135,10 +23135,10 @@
         </is>
       </c>
       <c r="L307" t="n">
-        <v>0.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M307" t="n">
-        <v>0.36</v>
+        <v>0.55</v>
       </c>
       <c r="N307" t="n">
         <v>0.78</v>
@@ -23147,19 +23147,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="P307" t="n">
-        <v>0.426</v>
+        <v>0.6005</v>
       </c>
       <c r="Q307" t="n">
         <v>1</v>
       </c>
       <c r="R307" t="n">
-        <v>12.01</v>
+        <v>8.07</v>
       </c>
       <c r="S307" t="n">
-        <v>2.28</v>
+        <v>1.53</v>
       </c>
       <c r="T307" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="308">
@@ -23209,10 +23209,10 @@
         </is>
       </c>
       <c r="L308" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="M308" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="N308" t="n">
         <v>0.7</v>
@@ -23221,7 +23221,7 @@
         <v>0.78</v>
       </c>
       <c r="P308" t="n">
-        <v>0.677</v>
+        <v>0.6185</v>
       </c>
       <c r="Q308" t="n">
         <v>3</v>
@@ -23283,10 +23283,10 @@
         </is>
       </c>
       <c r="L309" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M309" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="N309" t="n">
         <v>0.93</v>
@@ -23295,7 +23295,7 @@
         <v>0.78</v>
       </c>
       <c r="P309" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="Q309" t="n">
         <v>2</v>
@@ -23357,10 +23357,10 @@
         </is>
       </c>
       <c r="L310" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="M310" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="N310" t="n">
         <v>0.86</v>
@@ -23369,7 +23369,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="P310" t="n">
-        <v>0.762</v>
+        <v>0.7005</v>
       </c>
       <c r="Q310" t="n">
         <v>1</v>
@@ -23431,10 +23431,10 @@
         </is>
       </c>
       <c r="L311" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="M311" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="N311" t="n">
         <v>0.41</v>
@@ -23443,19 +23443,19 @@
         <v>0.78</v>
       </c>
       <c r="P311" t="n">
-        <v>0.8165</v>
+        <v>0.849</v>
       </c>
       <c r="Q311" t="n">
         <v>3</v>
       </c>
       <c r="R311" t="n">
-        <v>3.84</v>
+        <v>0.24</v>
       </c>
       <c r="S311" t="n">
-        <v>0.73</v>
+        <v>0.05</v>
       </c>
       <c r="T311" t="n">
-        <v>3.75</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="312">
@@ -23505,10 +23505,10 @@
         </is>
       </c>
       <c r="L312" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="M312" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="N312" t="n">
         <v>0.7</v>
@@ -23517,19 +23517,19 @@
         <v>0.78</v>
       </c>
       <c r="P312" t="n">
-        <v>0.8485</v>
+        <v>0.907</v>
       </c>
       <c r="Q312" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R312" t="n">
-        <v>4.44</v>
+        <v>0.84</v>
       </c>
       <c r="S312" t="n">
-        <v>0.84</v>
+        <v>0.16</v>
       </c>
       <c r="T312" t="n">
-        <v>4.33</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="313">
@@ -23579,10 +23579,10 @@
         </is>
       </c>
       <c r="L313" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="M313" t="n">
-        <v>0.87</v>
+        <v>0.97</v>
       </c>
       <c r="N313" t="n">
         <v>0.93</v>
@@ -23591,19 +23591,19 @@
         <v>0.66</v>
       </c>
       <c r="P313" t="n">
-        <v>0.8475</v>
+        <v>0.9155</v>
       </c>
       <c r="Q313" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R313" t="n">
-        <v>5.03</v>
+        <v>1.43</v>
       </c>
       <c r="S313" t="n">
-        <v>0.96</v>
+        <v>0.27</v>
       </c>
       <c r="T313" t="n">
-        <v>4.91</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="314">
@@ -23653,10 +23653,10 @@
         </is>
       </c>
       <c r="L314" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="M314" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="N314" t="n">
         <v>0.86</v>
@@ -23665,7 +23665,7 @@
         <v>0.89</v>
       </c>
       <c r="P314" t="n">
-        <v>0.9005</v>
+        <v>0.8225</v>
       </c>
       <c r="Q314" t="n">
         <v>3</v>
@@ -23727,10 +23727,10 @@
         </is>
       </c>
       <c r="L315" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="M315" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N315" t="n">
         <v>1</v>
@@ -23739,7 +23739,7 @@
         <v>0.89</v>
       </c>
       <c r="P315" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.857</v>
       </c>
       <c r="Q315" t="n">
         <v>1</v>
@@ -23801,10 +23801,10 @@
         </is>
       </c>
       <c r="L316" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M316" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="N316" t="n">
         <v>0.78</v>
@@ -23813,7 +23813,7 @@
         <v>0.92</v>
       </c>
       <c r="P316" t="n">
-        <v>0.905</v>
+        <v>0.8275</v>
       </c>
       <c r="Q316" t="n">
         <v>2</v>
